--- a/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
   <si>
     <t>HNVR</t>
   </si>
@@ -656,63 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -722,38 +723,44 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F8" s="3">
         <v>28500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>25100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>22600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>19600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>16300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>15900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>16600</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -763,8 +770,14 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -804,8 +817,14 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -845,8 +864,14 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +887,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,8 +930,14 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,8 +977,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -985,8 +1024,14 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1026,8 +1071,14 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1040,38 +1091,40 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F17" s="3">
         <v>15500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>12100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>8800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>5200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2200</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1081,38 +1134,44 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>11300</v>
+      </c>
+      <c r="F18" s="3">
         <v>13000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>13000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>13800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>14400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>13900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>14200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>14400</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1122,8 +1181,14 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1139,38 +1204,40 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-8600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-8900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-6800</v>
       </c>
       <c r="H20" s="3">
         <v>-6900</v>
       </c>
       <c r="I20" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="K20" s="3">
         <v>-6600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-5900</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,38 +1247,44 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>4600</v>
       </c>
       <c r="H21" s="3">
-        <v>8200</v>
+        <v>7300</v>
       </c>
       <c r="I21" s="3">
+        <v>8000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>7400</v>
+      </c>
+      <c r="K21" s="3">
         <v>8400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>8900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1221,8 +1294,14 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1262,38 +1341,44 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F23" s="3">
         <v>4400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>4200</v>
-      </c>
-      <c r="F23" s="3">
-        <v>6900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>7500</v>
       </c>
       <c r="H23" s="3">
         <v>6900</v>
       </c>
       <c r="I23" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J23" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K23" s="3">
         <v>7600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>8500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1303,8 +1388,14 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1312,13 +1403,13 @@
         <v>1300</v>
       </c>
       <c r="E24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G24" s="3">
         <v>1000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1700</v>
       </c>
       <c r="H24" s="3">
         <v>1600</v>
@@ -1327,14 +1418,14 @@
         <v>1700</v>
       </c>
       <c r="J24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1344,8 +1435,14 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1385,38 +1482,44 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F26" s="3">
         <v>3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3200</v>
-      </c>
-      <c r="F26" s="3">
-        <v>5300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>5800</v>
       </c>
       <c r="H26" s="3">
         <v>5300</v>
       </c>
       <c r="I26" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K26" s="3">
         <v>5900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>6500</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1426,38 +1529,44 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G27" s="3">
         <v>3100</v>
       </c>
-      <c r="E27" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I27" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J27" s="3">
         <v>5300</v>
       </c>
-      <c r="G27" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H27" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>5900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>6500</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1467,8 +1576,14 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1508,8 +1623,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1549,8 +1670,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +1717,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1631,38 +1764,44 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F32" s="3">
         <v>8600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>8900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>6900</v>
-      </c>
-      <c r="G32" s="3">
-        <v>6800</v>
       </c>
       <c r="H32" s="3">
         <v>6900</v>
       </c>
       <c r="I32" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J32" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K32" s="3">
         <v>6600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>5900</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1672,38 +1811,44 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F33" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G33" s="3">
         <v>3100</v>
       </c>
-      <c r="E33" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I33" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J33" s="3">
         <v>5300</v>
       </c>
-      <c r="G33" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H33" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>5900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>6500</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1713,8 +1858,14 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1754,38 +1905,44 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F35" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G35" s="3">
         <v>3100</v>
       </c>
-      <c r="E35" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I35" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J35" s="3">
         <v>5300</v>
       </c>
-      <c r="G35" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H35" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>5900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>6500</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1795,43 +1952,49 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1841,8 +2004,14 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1858,8 +2027,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1875,38 +2046,40 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>211500</v>
+        <v>10300</v>
       </c>
       <c r="E41" s="3">
-        <v>204400</v>
+        <v>5500</v>
       </c>
       <c r="F41" s="3">
-        <v>152300</v>
+        <v>5400</v>
       </c>
       <c r="G41" s="3">
-        <v>149900</v>
+        <v>9200</v>
       </c>
       <c r="H41" s="3">
+        <v>9500</v>
+      </c>
+      <c r="I41" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J41" s="3">
         <v>11900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7800</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1916,38 +2089,44 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>175500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>197700</v>
+      </c>
+      <c r="F42" s="3">
+        <v>221900</v>
+      </c>
+      <c r="G42" s="3">
+        <v>203200</v>
       </c>
       <c r="H42" s="3">
+        <v>155000</v>
+      </c>
+      <c r="I42" s="3">
+        <v>146300</v>
+      </c>
+      <c r="J42" s="3">
         <v>125900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>123800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>111200</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1957,8 +2136,14 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1998,8 +2183,14 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2039,8 +2230,14 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2080,8 +2277,14 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2121,8 +2324,14 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2162,38 +2371,44 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>26300</v>
+      </c>
+      <c r="F48" s="3">
         <v>26900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>26700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>26300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>14500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>14700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>14800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>14900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2203,25 +2418,31 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>19200</v>
+        <v>19500</v>
       </c>
       <c r="E49" s="3">
-        <v>19200</v>
+        <v>19500</v>
       </c>
       <c r="F49" s="3">
-        <v>19200</v>
+        <v>19500</v>
       </c>
       <c r="G49" s="3">
-        <v>19200</v>
+        <v>19500</v>
       </c>
       <c r="H49" s="3">
-        <v>19600</v>
+        <v>19500</v>
       </c>
       <c r="I49" s="3">
         <v>19600</v>
@@ -2229,11 +2450,11 @@
       <c r="J49" s="3">
         <v>19600</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>19600</v>
+      </c>
+      <c r="L49" s="3">
+        <v>19600</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2244,8 +2465,14 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2285,8 +2512,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2326,38 +2559,44 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="G52" s="3">
+        <v>5600</v>
       </c>
       <c r="H52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J52" s="3">
         <v>6300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>6900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>7300</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,8 +2606,14 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2408,38 +2653,44 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2270100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2149500</v>
+      </c>
+      <c r="F54" s="3">
         <v>2121800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2071700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1983700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1840100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1609800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1476700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1458200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,8 +2700,14 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2466,8 +2723,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2483,38 +2742,40 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1400</v>
       </c>
       <c r="H57" s="3">
+        <v>800</v>
+      </c>
+      <c r="I57" s="3">
+        <v>900</v>
+      </c>
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2524,8 +2785,14 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2545,17 +2812,17 @@
         <v>24600</v>
       </c>
       <c r="I58" s="3">
+        <v>24600</v>
+      </c>
+      <c r="J58" s="3">
+        <v>24600</v>
+      </c>
+      <c r="K58" s="3">
         <v>24500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>24500</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2565,26 +2832,32 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F59" s="3">
         <v>11300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>11700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>12100</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2597,17 +2870,23 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
-      <c r="N59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2647,8 +2926,14 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2688,8 +2973,14 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2729,8 +3020,14 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2770,8 +3067,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2811,8 +3114,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2852,38 +3161,44 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2085200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1963600</v>
+      </c>
+      <c r="F66" s="3">
         <v>1939000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1891200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1806100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1667500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1442400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1341900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1328800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2893,8 +3208,14 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2910,8 +3231,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2951,8 +3274,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2992,25 +3321,31 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -3033,8 +3368,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3074,38 +3415,44 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>58700</v>
+      </c>
+      <c r="F72" s="3">
+        <v>55900</v>
+      </c>
+      <c r="G72" s="3">
+        <v>53500</v>
       </c>
       <c r="H72" s="3">
+        <v>51100</v>
+      </c>
+      <c r="I72" s="3">
+        <v>46500</v>
+      </c>
+      <c r="J72" s="3">
         <v>41400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>36800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>31500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3115,8 +3462,14 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3156,8 +3509,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3197,8 +3556,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3238,38 +3603,44 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>182800</v>
+        <v>181900</v>
       </c>
       <c r="E76" s="3">
-        <v>180500</v>
+        <v>182900</v>
       </c>
       <c r="F76" s="3">
+        <v>179800</v>
+      </c>
+      <c r="G76" s="3">
         <v>177600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>174700</v>
+      </c>
+      <c r="I76" s="3">
         <v>172600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>167400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>134800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>129400</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3279,8 +3650,14 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3320,43 +3697,49 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3366,38 +3749,44 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F81" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G81" s="3">
         <v>3100</v>
       </c>
-      <c r="E81" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I81" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J81" s="3">
         <v>5300</v>
       </c>
-      <c r="G81" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H81" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>5900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>6500</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3407,8 +3796,14 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3424,31 +3819,33 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3456,17 +3853,23 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3506,8 +3909,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3547,8 +3956,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3588,8 +4003,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3629,8 +4050,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3670,31 +4097,37 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F89" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -3702,17 +4135,23 @@
       <c r="L89" s="3">
         <v>0</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3728,31 +4167,33 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3760,17 +4201,23 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3810,8 +4257,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3851,31 +4304,37 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-137400</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-46600</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-43400</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
+        <v>-36900</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>-129400</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
+        <v>-214700</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>-128300</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -3883,17 +4342,23 @@
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3909,31 +4374,33 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3950,8 +4417,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3991,8 +4464,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4032,8 +4511,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4073,31 +4558,37 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>117800</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>26800</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>42600</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>87600</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>125600</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>222900</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>127700</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -4105,17 +4596,23 @@
       <c r="L100" s="3">
         <v>0</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4155,31 +4652,37 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-15400</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-18900</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>52100</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -4187,13 +4690,19 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>HNVR</t>
   </si>
@@ -656,67 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -729,41 +730,44 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E8" s="3">
         <v>31200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>29000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16600</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -776,8 +780,11 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -823,8 +830,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -870,8 +880,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,8 +902,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -936,8 +950,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,8 +1000,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1030,8 +1050,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1077,8 +1100,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1093,41 +1119,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E17" s="3">
         <v>18700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1140,41 +1167,44 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E18" s="3">
         <v>12500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>11300</v>
-      </c>
-      <c r="F18" s="3">
-        <v>13000</v>
       </c>
       <c r="G18" s="3">
         <v>13000</v>
       </c>
       <c r="H18" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I18" s="3">
         <v>13800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14400</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1187,8 +1217,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1206,41 +1239,42 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5900</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1253,41 +1287,44 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1300,8 +1337,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1347,41 +1387,44 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E23" s="3">
         <v>5000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1394,8 +1437,11 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1403,32 +1449,32 @@
         <v>1300</v>
       </c>
       <c r="E24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1900</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1441,8 +1487,11 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1488,41 +1537,44 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E26" s="3">
         <v>3800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6500</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1535,41 +1587,44 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E27" s="3">
         <v>3600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6500</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1582,8 +1637,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1629,8 +1687,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1676,8 +1737,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1723,8 +1787,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1770,41 +1837,44 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E32" s="3">
         <v>7500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5900</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1817,41 +1887,44 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E33" s="3">
         <v>3600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6500</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,8 +1937,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1911,41 +1987,44 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E35" s="3">
         <v>3600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6500</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1958,46 +2037,49 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2010,8 +2092,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2029,8 +2114,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2048,41 +2134,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E41" s="3">
         <v>10300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7800</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,41 +2182,44 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>139700</v>
+      </c>
+      <c r="E42" s="3">
         <v>175500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>197700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>221900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>203200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>155000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>146300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>125900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>123800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>111200</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2142,8 +2232,11 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2189,8 +2282,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2236,8 +2332,11 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2283,8 +2382,11 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2330,8 +2432,11 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2377,41 +2482,44 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E48" s="3">
         <v>25600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14900</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2424,8 +2532,11 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2445,7 +2556,7 @@
         <v>19500</v>
       </c>
       <c r="I49" s="3">
-        <v>19600</v>
+        <v>19500</v>
       </c>
       <c r="J49" s="3">
         <v>19600</v>
@@ -2456,8 +2567,8 @@
       <c r="L49" s="3">
         <v>19600</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>19600</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -2471,8 +2582,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2518,8 +2632,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2565,41 +2682,44 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E52" s="3">
         <v>6000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>6000</v>
       </c>
       <c r="I52" s="3">
         <v>6000</v>
       </c>
       <c r="J52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K52" s="3">
         <v>6300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7300</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2612,8 +2732,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2659,41 +2782,44 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2307500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2270100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2149500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2121800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2071700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1983700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1840100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1609800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1476700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1458200</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2706,8 +2832,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2725,8 +2854,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2744,41 +2874,42 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,8 +2922,11 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2818,13 +2952,13 @@
         <v>24600</v>
       </c>
       <c r="K58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="L58" s="3">
         <v>24500</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>24500</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -2838,29 +2972,32 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E59" s="3">
         <v>10500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2876,8 +3013,8 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -2885,8 +3022,11 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2932,8 +3072,11 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2979,8 +3122,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3026,8 +3172,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3073,8 +3222,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3120,8 +3272,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3167,41 +3322,44 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2118000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2085200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1963600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1939000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1891200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1806100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1667500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1442400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1341900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1328800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3214,8 +3372,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3233,8 +3394,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3280,8 +3442,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3327,8 +3492,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3348,7 +3516,7 @@
         <v>3000</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -3374,8 +3542,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3421,41 +3592,44 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E72" s="3">
         <v>58600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>58700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>55900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>53500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>51100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>46500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>41400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>36800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>31500</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3468,8 +3642,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3515,8 +3692,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3562,8 +3742,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3609,41 +3792,44 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>186600</v>
+      </c>
+      <c r="E76" s="3">
         <v>181900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>182900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>179800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>177600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>174700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>172600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>167400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>134800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>129400</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3656,8 +3842,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3703,46 +3892,49 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3755,41 +3947,44 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E81" s="3">
         <v>3600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6500</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3802,8 +3997,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3821,13 +4019,14 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E83" s="3">
         <v>500</v>
@@ -3836,7 +4035,7 @@
         <v>500</v>
       </c>
       <c r="G83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H83" s="3">
         <v>400</v>
@@ -3848,7 +4047,7 @@
         <v>400</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -3859,8 +4058,8 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -3868,8 +4067,11 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3915,8 +4117,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3962,8 +4167,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4009,8 +4217,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4056,8 +4267,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4103,35 +4317,38 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E89" s="3">
         <v>4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7500</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
@@ -4141,8 +4358,8 @@
       <c r="N89" s="3">
         <v>0</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
+      <c r="O89" s="3">
+        <v>0</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
@@ -4150,8 +4367,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4169,35 +4389,36 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -4207,8 +4428,8 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4216,8 +4437,11 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4263,8 +4487,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4310,35 +4537,38 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-76200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-137400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-46600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-43400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-36900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-129400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-214700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-128300</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
@@ -4348,8 +4578,8 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
@@ -4357,8 +4587,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4376,8 +4609,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4403,7 +4637,7 @@
         <v>-700</v>
       </c>
       <c r="K96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4423,8 +4657,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4470,8 +4707,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4517,8 +4757,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4564,35 +4807,38 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E100" s="3">
         <v>117800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>26800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>42600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>87600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>125600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>222900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>127700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -4602,8 +4848,8 @@
       <c r="N100" s="3">
         <v>0</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
@@ -4611,8 +4857,11 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4658,35 +4907,38 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>52100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6800</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
@@ -4696,13 +4948,16 @@
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>HNVR</t>
   </si>
@@ -656,71 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -733,44 +734,47 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E8" s="3">
         <v>32400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>31200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>29000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>28500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16600</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -783,8 +787,11 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -833,8 +840,11 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -883,8 +893,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,8 +916,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -953,8 +967,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1003,8 +1020,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1053,8 +1073,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1103,8 +1126,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1120,44 +1146,45 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E17" s="3">
         <v>19800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1170,44 +1197,47 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E18" s="3">
         <v>12600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>11300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>13000</v>
       </c>
       <c r="H18" s="3">
         <v>13000</v>
       </c>
       <c r="I18" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J18" s="3">
         <v>13800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14400</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1220,8 +1250,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1240,44 +1273,45 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5900</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1290,44 +1324,47 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E21" s="3">
         <v>6000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1340,8 +1377,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1390,44 +1430,47 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E23" s="3">
         <v>5400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8500</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,44 +1483,47 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1300</v>
+        <v>300</v>
       </c>
       <c r="E24" s="3">
         <v>1300</v>
       </c>
       <c r="F24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1490,8 +1536,11 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1540,44 +1589,47 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>800</v>
+      </c>
+      <c r="E26" s="3">
         <v>4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6500</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1590,44 +1642,47 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>800</v>
+      </c>
+      <c r="E27" s="3">
         <v>3900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6500</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1640,8 +1695,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1690,8 +1748,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1740,8 +1801,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1790,8 +1854,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1840,44 +1907,47 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E32" s="3">
         <v>7200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5900</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1890,44 +1960,47 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>800</v>
+      </c>
+      <c r="E33" s="3">
         <v>3900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6500</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1940,8 +2013,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1990,44 +2066,47 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>800</v>
+      </c>
+      <c r="E35" s="3">
         <v>3900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6500</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2040,49 +2119,52 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2095,8 +2177,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2115,8 +2200,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2135,44 +2221,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E41" s="3">
         <v>5400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7800</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2185,44 +2272,47 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>142300</v>
+      </c>
+      <c r="E42" s="3">
         <v>139700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>175500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>197700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>221900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>203200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>155000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>146300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>125900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>123800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>111200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2235,8 +2325,11 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2285,8 +2378,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2335,8 +2431,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2385,8 +2484,11 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2435,8 +2537,11 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2485,44 +2590,47 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E48" s="3">
         <v>25000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>25600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14900</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2535,13 +2643,16 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>19500</v>
+        <v>19400</v>
       </c>
       <c r="E49" s="3">
         <v>19500</v>
@@ -2559,7 +2670,7 @@
         <v>19500</v>
       </c>
       <c r="J49" s="3">
-        <v>19600</v>
+        <v>19500</v>
       </c>
       <c r="K49" s="3">
         <v>19600</v>
@@ -2570,8 +2681,8 @@
       <c r="M49" s="3">
         <v>19600</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="N49" s="3">
+        <v>19600</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
@@ -2585,8 +2696,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2635,8 +2749,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2685,44 +2802,47 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E52" s="3">
         <v>5700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>6000</v>
       </c>
       <c r="J52" s="3">
         <v>6000</v>
       </c>
       <c r="K52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="L52" s="3">
         <v>6300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7300</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2735,8 +2855,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2785,44 +2908,47 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2331100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2307500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2270100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2149500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2121800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2071700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1983700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1840100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1609800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1476700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1458200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,8 +2961,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2855,8 +2984,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2875,44 +3005,45 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,13 +3056,16 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>24600</v>
+        <v>24700</v>
       </c>
       <c r="E58" s="3">
         <v>24600</v>
@@ -2955,13 +3089,13 @@
         <v>24600</v>
       </c>
       <c r="L58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="M58" s="3">
         <v>24500</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="N58" s="3">
+        <v>24500</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
@@ -2975,32 +3109,35 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E59" s="3">
         <v>10000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3016,8 +3153,8 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
@@ -3025,8 +3162,11 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3075,8 +3215,11 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3125,8 +3268,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3175,8 +3321,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3225,8 +3374,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3275,8 +3427,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3325,44 +3480,47 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2141000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2118000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2085200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1963600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1939000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1891200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1806100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1667500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1442400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1341900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1328800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3375,8 +3533,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3395,8 +3556,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3445,8 +3607,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3495,13 +3660,16 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="E70" s="3">
         <v>3000</v>
@@ -3519,7 +3687,7 @@
         <v>3000</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -3545,8 +3713,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3595,44 +3766,47 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E72" s="3">
         <v>61900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>58600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>55900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>53500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>51100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>46500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>41400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>36800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>31500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3819,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3695,8 +3872,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3745,8 +3925,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3795,44 +3978,47 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E76" s="3">
         <v>186600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>181900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>182900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>179800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>177600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>174700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>172600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>167400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>134800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>129400</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3845,8 +4031,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3895,49 +4084,52 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3950,44 +4142,47 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>800</v>
+      </c>
+      <c r="E81" s="3">
         <v>3900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6500</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4000,8 +4195,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4020,8 +4218,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4029,7 +4228,7 @@
         <v>600</v>
       </c>
       <c r="E83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F83" s="3">
         <v>500</v>
@@ -4038,7 +4237,7 @@
         <v>500</v>
       </c>
       <c r="H83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I83" s="3">
         <v>400</v>
@@ -4050,7 +4249,7 @@
         <v>400</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -4061,8 +4260,8 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4070,8 +4269,11 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4120,8 +4322,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4170,8 +4375,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4220,8 +4428,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4270,8 +4481,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4320,38 +4534,41 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E89" s="3">
         <v>3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7500</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
@@ -4361,8 +4578,8 @@
       <c r="O89" s="3">
         <v>0</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
@@ -4370,8 +4587,11 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4390,38 +4610,39 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -4431,8 +4652,8 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4440,8 +4661,11 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4490,8 +4714,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4540,38 +4767,41 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-76200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-137400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-46600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-43400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-36900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-129400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-214700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-128300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
@@ -4581,8 +4811,8 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -4590,8 +4820,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4610,8 +4843,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4640,7 +4874,7 @@
         <v>-700</v>
       </c>
       <c r="L96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4660,8 +4894,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4710,8 +4947,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4760,8 +5000,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4810,38 +5053,41 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E100" s="3">
         <v>31900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>117800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>26800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>42600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>87600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>125600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>222900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>127700</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -4851,8 +5097,8 @@
       <c r="O100" s="3">
         <v>0</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
@@ -4860,8 +5106,11 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4910,38 +5159,41 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-40700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>52100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6800</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
@@ -4951,13 +5203,16 @@
       <c r="O102" s="3">
         <v>0</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
   <si>
     <t>HNVR</t>
   </si>
@@ -656,75 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45291</v>
       </c>
       <c r="G7" s="2">
         <v>45199</v>
       </c>
       <c r="H7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
       <c r="J7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -737,47 +737,50 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>33400</v>
+        <v>16900</v>
       </c>
       <c r="E8" s="3">
-        <v>32400</v>
+        <v>12800</v>
       </c>
       <c r="F8" s="3">
-        <v>31200</v>
+        <v>16200</v>
       </c>
       <c r="G8" s="3">
-        <v>29000</v>
+        <v>15000</v>
       </c>
       <c r="H8" s="3">
-        <v>28500</v>
+        <v>15000</v>
       </c>
       <c r="I8" s="3">
-        <v>25100</v>
+        <v>15000</v>
       </c>
       <c r="J8" s="3">
+        <v>15000</v>
+      </c>
+      <c r="K8" s="3">
         <v>22600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16600</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -790,8 +793,11 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -843,31 +849,34 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F10" s="3">
+        <v>16200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>15000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>15000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -896,8 +905,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -917,8 +929,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -970,8 +983,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1023,31 +1039,34 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1076,31 +1095,34 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1129,8 +1151,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1147,47 +1172,48 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>24200</v>
+        <v>11900</v>
       </c>
       <c r="E17" s="3">
-        <v>19800</v>
+        <v>11300</v>
       </c>
       <c r="F17" s="3">
-        <v>18700</v>
+        <v>10500</v>
       </c>
       <c r="G17" s="3">
-        <v>17700</v>
+        <v>9900</v>
       </c>
       <c r="H17" s="3">
-        <v>15500</v>
+        <v>9900</v>
       </c>
       <c r="I17" s="3">
-        <v>12100</v>
+        <v>10200</v>
       </c>
       <c r="J17" s="3">
+        <v>10200</v>
+      </c>
+      <c r="K17" s="3">
         <v>8800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1200,47 +1226,50 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>9200</v>
+        <v>5000</v>
       </c>
       <c r="E18" s="3">
-        <v>12600</v>
+        <v>1500</v>
       </c>
       <c r="F18" s="3">
-        <v>12500</v>
+        <v>5700</v>
       </c>
       <c r="G18" s="3">
-        <v>11300</v>
+        <v>5100</v>
       </c>
       <c r="H18" s="3">
-        <v>13000</v>
+        <v>5100</v>
       </c>
       <c r="I18" s="3">
-        <v>13000</v>
+        <v>4800</v>
       </c>
       <c r="J18" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K18" s="3">
         <v>13800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14400</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1253,8 +1282,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1274,47 +1306,48 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-8000</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
-        <v>-7200</v>
+        <v>400</v>
       </c>
       <c r="F20" s="3">
-        <v>-7500</v>
+        <v>300</v>
       </c>
       <c r="G20" s="3">
-        <v>-6700</v>
+        <v>400</v>
       </c>
       <c r="H20" s="3">
-        <v>-8600</v>
+        <v>400</v>
       </c>
       <c r="I20" s="3">
-        <v>-8900</v>
+        <v>400</v>
       </c>
       <c r="J20" s="3">
+        <v>400</v>
+      </c>
+      <c r="K20" s="3">
         <v>-6900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5900</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1327,47 +1360,50 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E21" s="3">
         <v>1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>5600</v>
       </c>
       <c r="G21" s="3">
         <v>5200</v>
       </c>
       <c r="H21" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I21" s="3">
         <v>4900</v>
       </c>
-      <c r="I21" s="3">
-        <v>4600</v>
-      </c>
       <c r="J21" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K21" s="3">
         <v>7300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1380,31 +1416,34 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1433,47 +1472,50 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E23" s="3">
         <v>1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5400</v>
-      </c>
-      <c r="F23" s="3">
-        <v>5000</v>
       </c>
       <c r="G23" s="3">
         <v>4700</v>
       </c>
       <c r="H23" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I23" s="3">
         <v>4400</v>
       </c>
-      <c r="I23" s="3">
-        <v>4200</v>
-      </c>
       <c r="J23" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K23" s="3">
         <v>6900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1486,16 +1528,19 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
-      </c>
-      <c r="E24" s="3">
-        <v>1300</v>
       </c>
       <c r="F24" s="3">
         <v>1300</v>
@@ -1504,29 +1549,29 @@
         <v>1200</v>
       </c>
       <c r="H24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I24" s="3">
         <v>1300</v>
       </c>
-      <c r="I24" s="3">
-        <v>1000</v>
-      </c>
       <c r="J24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K24" s="3">
         <v>1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,8 +1584,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1592,47 +1640,50 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E26" s="3">
         <v>800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4100</v>
-      </c>
-      <c r="F26" s="3">
-        <v>3800</v>
       </c>
       <c r="G26" s="3">
         <v>3500</v>
       </c>
       <c r="H26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I26" s="3">
         <v>3100</v>
       </c>
-      <c r="I26" s="3">
-        <v>3200</v>
-      </c>
       <c r="J26" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K26" s="3">
         <v>5300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6500</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1645,47 +1696,50 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E27" s="3">
         <v>800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>3600</v>
       </c>
       <c r="G27" s="3">
         <v>3400</v>
       </c>
       <c r="H27" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I27" s="3">
         <v>3000</v>
       </c>
-      <c r="I27" s="3">
-        <v>3100</v>
-      </c>
       <c r="J27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K27" s="3">
         <v>5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6500</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,8 +1752,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1751,8 +1808,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1804,8 +1864,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1857,8 +1920,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1910,47 +1976,50 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>8000</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
-        <v>7200</v>
+        <v>-400</v>
       </c>
       <c r="F32" s="3">
-        <v>7500</v>
+        <v>-300</v>
       </c>
       <c r="G32" s="3">
-        <v>6700</v>
+        <v>-400</v>
       </c>
       <c r="H32" s="3">
-        <v>8600</v>
+        <v>-400</v>
       </c>
       <c r="I32" s="3">
-        <v>8900</v>
+        <v>-400</v>
       </c>
       <c r="J32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K32" s="3">
         <v>6900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5900</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1963,47 +2032,50 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E33" s="3">
         <v>800</v>
       </c>
-      <c r="E33" s="3">
-        <v>3900</v>
-      </c>
       <c r="F33" s="3">
-        <v>3600</v>
+        <v>4100</v>
       </c>
       <c r="G33" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="H33" s="3">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="I33" s="3">
         <v>3100</v>
       </c>
       <c r="J33" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K33" s="3">
         <v>5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6500</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2016,8 +2088,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2069,47 +2144,50 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E35" s="3">
         <v>800</v>
       </c>
-      <c r="E35" s="3">
-        <v>3900</v>
-      </c>
       <c r="F35" s="3">
-        <v>3600</v>
+        <v>4100</v>
       </c>
       <c r="G35" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="H35" s="3">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="I35" s="3">
         <v>3100</v>
       </c>
       <c r="J35" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K35" s="3">
         <v>5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6500</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,52 +2200,55 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45291</v>
       </c>
       <c r="G38" s="2">
         <v>45199</v>
       </c>
       <c r="H38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
       <c r="J38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2180,8 +2261,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2201,8 +2285,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2222,47 +2307,48 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8400</v>
+        <v>141200</v>
       </c>
       <c r="E41" s="3">
-        <v>5400</v>
+        <v>141100</v>
       </c>
       <c r="F41" s="3">
-        <v>10300</v>
+        <v>136500</v>
       </c>
       <c r="G41" s="3">
-        <v>5500</v>
+        <v>192600</v>
       </c>
       <c r="H41" s="3">
-        <v>5400</v>
+        <v>192600</v>
       </c>
       <c r="I41" s="3">
-        <v>9200</v>
+        <v>211500</v>
       </c>
       <c r="J41" s="3">
+        <v>211500</v>
+      </c>
+      <c r="K41" s="3">
         <v>9500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,47 +2361,50 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>142300</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>139700</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
-        <v>175500</v>
+        <v>200</v>
       </c>
       <c r="G42" s="3">
-        <v>197700</v>
+        <v>400</v>
       </c>
       <c r="H42" s="3">
-        <v>221900</v>
+        <v>400</v>
       </c>
       <c r="I42" s="3">
-        <v>203200</v>
+        <v>100</v>
       </c>
       <c r="J42" s="3">
+        <v>100</v>
+      </c>
+      <c r="K42" s="3">
         <v>155000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>146300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>125900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>123800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>111200</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2328,31 +2417,34 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2381,31 +2473,34 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2434,31 +2529,34 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>12400</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>10600</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>10600</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2487,31 +2585,34 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>170500</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>165500</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>156700</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>203700</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>203700</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>221900</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>221900</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2540,31 +2641,34 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>110700</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>112300</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>105300</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2593,47 +2697,50 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E48" s="3">
         <v>25800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>25000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>25600</v>
       </c>
       <c r="G48" s="3">
         <v>26300</v>
       </c>
       <c r="H48" s="3">
+        <v>26300</v>
+      </c>
+      <c r="I48" s="3">
         <v>26900</v>
       </c>
-      <c r="I48" s="3">
-        <v>26700</v>
-      </c>
       <c r="J48" s="3">
+        <v>26900</v>
+      </c>
+      <c r="K48" s="3">
         <v>26300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,34 +2753,37 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>19400</v>
+        <v>25200</v>
       </c>
       <c r="E49" s="3">
+        <v>24900</v>
+      </c>
+      <c r="F49" s="3">
+        <v>24600</v>
+      </c>
+      <c r="G49" s="3">
+        <v>24000</v>
+      </c>
+      <c r="H49" s="3">
+        <v>24000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>23900</v>
+      </c>
+      <c r="J49" s="3">
+        <v>23900</v>
+      </c>
+      <c r="K49" s="3">
         <v>19500</v>
-      </c>
-      <c r="F49" s="3">
-        <v>19500</v>
-      </c>
-      <c r="G49" s="3">
-        <v>19500</v>
-      </c>
-      <c r="H49" s="3">
-        <v>19500</v>
-      </c>
-      <c r="I49" s="3">
-        <v>19500</v>
-      </c>
-      <c r="J49" s="3">
-        <v>19500</v>
-      </c>
-      <c r="K49" s="3">
-        <v>19600</v>
       </c>
       <c r="L49" s="3">
         <v>19600</v>
@@ -2684,8 +2794,8 @@
       <c r="N49" s="3">
         <v>19600</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>19600</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
@@ -2699,8 +2809,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2752,8 +2865,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2805,47 +2921,50 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5600</v>
+        <v>11500</v>
       </c>
       <c r="E52" s="3">
-        <v>5700</v>
+        <v>11200</v>
       </c>
       <c r="F52" s="3">
-        <v>6000</v>
+        <v>8200</v>
       </c>
       <c r="G52" s="3">
-        <v>5000</v>
+        <v>8700</v>
       </c>
       <c r="H52" s="3">
-        <v>5500</v>
+        <v>8700</v>
       </c>
       <c r="I52" s="3">
-        <v>5600</v>
+        <v>8100</v>
       </c>
       <c r="J52" s="3">
-        <v>6000</v>
+        <v>8100</v>
       </c>
       <c r="K52" s="3">
         <v>6000</v>
       </c>
       <c r="L52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M52" s="3">
         <v>6300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7300</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2977,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2911,47 +3033,50 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2327800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2331100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2307500</v>
-      </c>
-      <c r="F54" s="3">
-        <v>2270100</v>
       </c>
       <c r="G54" s="3">
         <v>2149500</v>
       </c>
       <c r="H54" s="3">
+        <v>2149500</v>
+      </c>
+      <c r="I54" s="3">
         <v>2121800</v>
       </c>
-      <c r="I54" s="3">
-        <v>2071700</v>
-      </c>
       <c r="J54" s="3">
+        <v>2121800</v>
+      </c>
+      <c r="K54" s="3">
         <v>1983700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1840100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1609800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1476700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1458200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2964,8 +3089,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2985,8 +3113,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3006,47 +3135,48 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1600</v>
+        <v>1957500</v>
       </c>
       <c r="E57" s="3">
-        <v>2000</v>
+        <v>1941900</v>
       </c>
       <c r="F57" s="3">
-        <v>1700</v>
+        <v>1917300</v>
       </c>
       <c r="G57" s="3">
-        <v>1800</v>
+        <v>1735100</v>
       </c>
       <c r="H57" s="3">
-        <v>1200</v>
+        <v>1735100</v>
       </c>
       <c r="I57" s="3">
-        <v>1400</v>
+        <v>1593600</v>
       </c>
       <c r="J57" s="3">
+        <v>1593600</v>
+      </c>
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3059,31 +3189,34 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>24700</v>
+        <v>20700</v>
       </c>
       <c r="E58" s="3">
-        <v>24600</v>
+        <v>40900</v>
       </c>
       <c r="F58" s="3">
-        <v>24600</v>
+        <v>18900</v>
       </c>
       <c r="G58" s="3">
-        <v>24600</v>
+        <v>70000</v>
       </c>
       <c r="H58" s="3">
-        <v>24600</v>
+        <v>70000</v>
       </c>
       <c r="I58" s="3">
-        <v>24600</v>
+        <v>160000</v>
       </c>
       <c r="J58" s="3">
-        <v>24600</v>
+        <v>160000</v>
       </c>
       <c r="K58" s="3">
         <v>24600</v>
@@ -3092,13 +3225,13 @@
         <v>24600</v>
       </c>
       <c r="M58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="N58" s="3">
         <v>24500</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3">
+        <v>24500</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
@@ -3112,35 +3245,38 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>9900</v>
-      </c>
-      <c r="E59" s="3">
-        <v>10000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>10500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>10900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>11300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>11700</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>12100</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3156,8 +3292,8 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -3165,31 +3301,34 @@
       <c r="S59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1980100</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1984500</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1938200</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1806900</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1806900</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1754900</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1754900</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3218,31 +3357,34 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>142000</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>142600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>164800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>145400</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>145400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>169800</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>169800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3271,31 +3413,34 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>13900</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>14300</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>14300</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3324,8 +3469,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3377,8 +3525,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3430,8 +3581,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3483,47 +3637,50 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2135500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2141000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2118000</v>
-      </c>
-      <c r="F66" s="3">
-        <v>2085200</v>
       </c>
       <c r="G66" s="3">
         <v>1963600</v>
       </c>
       <c r="H66" s="3">
+        <v>1963600</v>
+      </c>
+      <c r="I66" s="3">
         <v>1939000</v>
       </c>
-      <c r="I66" s="3">
-        <v>1891200</v>
-      </c>
       <c r="J66" s="3">
+        <v>1939000</v>
+      </c>
+      <c r="K66" s="3">
         <v>1806100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1667500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1442400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1341900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1328800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,8 +3693,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3557,8 +3717,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3610,8 +3771,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3663,8 +3827,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3672,7 +3839,7 @@
         <v>5000</v>
       </c>
       <c r="E70" s="3">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="F70" s="3">
         <v>3000</v>
@@ -3690,7 +3857,7 @@
         <v>3000</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -3716,8 +3883,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3769,47 +3939,50 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E72" s="3">
         <v>62000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>61900</v>
-      </c>
-      <c r="F72" s="3">
-        <v>58600</v>
       </c>
       <c r="G72" s="3">
         <v>58700</v>
       </c>
       <c r="H72" s="3">
+        <v>58700</v>
+      </c>
+      <c r="I72" s="3">
         <v>55900</v>
       </c>
-      <c r="I72" s="3">
-        <v>53500</v>
-      </c>
       <c r="J72" s="3">
+        <v>55900</v>
+      </c>
+      <c r="K72" s="3">
         <v>51100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>46500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>41400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>36800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>31500</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3822,8 +3995,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3875,8 +4051,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3928,8 +4107,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3981,47 +4163,50 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>187300</v>
+      </c>
+      <c r="E76" s="3">
         <v>185000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>186600</v>
-      </c>
-      <c r="F76" s="3">
-        <v>181900</v>
       </c>
       <c r="G76" s="3">
         <v>182900</v>
       </c>
       <c r="H76" s="3">
+        <v>182900</v>
+      </c>
+      <c r="I76" s="3">
         <v>179800</v>
       </c>
-      <c r="I76" s="3">
-        <v>177600</v>
-      </c>
       <c r="J76" s="3">
+        <v>179800</v>
+      </c>
+      <c r="K76" s="3">
         <v>174700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>172600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>167400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>134800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>129400</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4034,8 +4219,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4087,52 +4275,55 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45291</v>
       </c>
       <c r="G80" s="2">
         <v>45199</v>
       </c>
       <c r="H80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
       <c r="J80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4145,47 +4336,50 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E81" s="3">
         <v>800</v>
       </c>
-      <c r="E81" s="3">
-        <v>3900</v>
-      </c>
       <c r="F81" s="3">
-        <v>3600</v>
+        <v>4100</v>
       </c>
       <c r="G81" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="H81" s="3">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="I81" s="3">
         <v>3100</v>
       </c>
       <c r="J81" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K81" s="3">
         <v>5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6500</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,8 +4392,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4219,25 +4416,26 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>2100</v>
       </c>
       <c r="E83" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="F83" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="G83" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="I83" s="3">
         <v>400</v>
@@ -4252,7 +4450,7 @@
         <v>400</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -4263,8 +4461,8 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4272,8 +4470,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4325,8 +4526,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4378,8 +4582,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4431,8 +4638,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4484,8 +4694,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4537,41 +4750,44 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3600</v>
-      </c>
-      <c r="F89" s="3">
-        <v>4100</v>
       </c>
       <c r="G89" s="3">
         <v>900</v>
       </c>
       <c r="H89" s="3">
+        <v>900</v>
+      </c>
+      <c r="I89" s="3">
         <v>8000</v>
       </c>
-      <c r="I89" s="3">
-        <v>1400</v>
-      </c>
       <c r="J89" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K89" s="3">
         <v>6100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7500</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
         <v>0</v>
       </c>
@@ -4581,8 +4797,8 @@
       <c r="P89" s="3">
         <v>0</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
@@ -4590,8 +4806,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4611,41 +4830,42 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="G91" s="3">
         <v>-300</v>
       </c>
       <c r="H91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
-        <v>-1200</v>
-      </c>
       <c r="J91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -4655,8 +4875,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -4664,8 +4884,11 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4717,8 +4940,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4770,41 +4996,44 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-76200</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-137400</v>
       </c>
       <c r="G94" s="3">
         <v>-46600</v>
       </c>
       <c r="H94" s="3">
+        <v>-46600</v>
+      </c>
+      <c r="I94" s="3">
         <v>-43400</v>
       </c>
-      <c r="I94" s="3">
-        <v>-36900</v>
-      </c>
       <c r="J94" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-129400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-214700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-128300</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -4814,8 +5043,8 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -4823,8 +5052,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4844,31 +5076,32 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="E96" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="F96" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="G96" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="H96" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="I96" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="J96" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="K96" s="3">
         <v>-700</v>
@@ -4877,7 +5110,7 @@
         <v>-700</v>
       </c>
       <c r="M96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4897,8 +5130,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4950,8 +5186,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5003,8 +5242,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5056,41 +5298,44 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E100" s="3">
         <v>24100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>31900</v>
-      </c>
-      <c r="F100" s="3">
-        <v>117800</v>
       </c>
       <c r="G100" s="3">
         <v>26800</v>
       </c>
       <c r="H100" s="3">
+        <v>26800</v>
+      </c>
+      <c r="I100" s="3">
         <v>42600</v>
       </c>
-      <c r="I100" s="3">
-        <v>87600</v>
-      </c>
       <c r="J100" s="3">
+        <v>42600</v>
+      </c>
+      <c r="K100" s="3">
         <v>125600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>222900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>127700</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -5100,8 +5345,8 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
@@ -5109,31 +5354,34 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5162,41 +5410,44 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>4600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-40700</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-15400</v>
       </c>
       <c r="G102" s="3">
         <v>-18900</v>
       </c>
       <c r="H102" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="I102" s="3">
         <v>7200</v>
       </c>
-      <c r="I102" s="3">
-        <v>52100</v>
-      </c>
       <c r="J102" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K102" s="3">
         <v>2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>16000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6800</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
@@ -5206,13 +5457,16 @@
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
   <si>
     <t>HNVR</t>
   </si>
@@ -656,78 +656,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
-        <v>45199</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
-        <v>45107</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -740,50 +740,53 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E8" s="3">
         <v>16900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16200</v>
       </c>
-      <c r="G8" s="3">
-        <v>15000</v>
-      </c>
       <c r="H8" s="3">
-        <v>15000</v>
+        <v>15700</v>
       </c>
       <c r="I8" s="3">
-        <v>15000</v>
+        <v>15700</v>
       </c>
       <c r="J8" s="3">
         <v>15000</v>
       </c>
       <c r="K8" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L8" s="3">
         <v>22600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16600</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -796,8 +799,11 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -852,34 +858,37 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E10" s="3">
         <v>16900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>16200</v>
       </c>
-      <c r="G10" s="3">
-        <v>15000</v>
-      </c>
       <c r="H10" s="3">
-        <v>15000</v>
+        <v>15700</v>
       </c>
       <c r="I10" s="3">
-        <v>15000</v>
+        <v>15700</v>
       </c>
       <c r="J10" s="3">
         <v>15000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
+      <c r="K10" s="3">
+        <v>15000</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
@@ -908,8 +917,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -930,8 +942,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -986,8 +999,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1042,8 +1058,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1059,17 +1078,17 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-1000</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1098,8 +1117,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1107,13 +1129,13 @@
         <v>500</v>
       </c>
       <c r="E15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
         <v>600</v>
       </c>
       <c r="G15" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H15" s="3">
         <v>500</v>
@@ -1125,7 +1147,7 @@
         <v>500</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1154,8 +1176,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1173,50 +1198,51 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E17" s="3">
         <v>11900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>10300</v>
+      </c>
+      <c r="I17" s="3">
+        <v>10300</v>
+      </c>
+      <c r="J17" s="3">
         <v>9900</v>
       </c>
-      <c r="H17" s="3">
-        <v>9900</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>10200</v>
       </c>
-      <c r="J17" s="3">
-        <v>10200</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2200</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1229,50 +1255,53 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E18" s="3">
         <v>5000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I18" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J18" s="3">
         <v>5100</v>
       </c>
-      <c r="H18" s="3">
-        <v>5100</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>4800</v>
       </c>
-      <c r="J18" s="3">
-        <v>4800</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14400</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1285,8 +1314,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1307,8 +1339,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1319,10 +1352,10 @@
         <v>400</v>
       </c>
       <c r="F20" s="3">
+        <v>400</v>
+      </c>
+      <c r="G20" s="3">
         <v>300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>400</v>
       </c>
       <c r="H20" s="3">
         <v>400</v>
@@ -1334,23 +1367,23 @@
         <v>400</v>
       </c>
       <c r="K20" s="3">
+        <v>400</v>
+      </c>
+      <c r="L20" s="3">
         <v>-6900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5900</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1363,50 +1396,53 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E21" s="3">
         <v>5100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J21" s="3">
         <v>5200</v>
       </c>
-      <c r="H21" s="3">
-        <v>5200</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>4900</v>
       </c>
-      <c r="J21" s="3">
-        <v>4900</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1419,8 +1455,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1445,8 +1484,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1475,50 +1514,53 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E23" s="3">
         <v>4600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J23" s="3">
         <v>4700</v>
       </c>
-      <c r="H23" s="3">
-        <v>4700</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>4400</v>
       </c>
-      <c r="J23" s="3">
-        <v>4400</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8500</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1531,50 +1573,53 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
-        <v>1200</v>
-      </c>
       <c r="H24" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="I24" s="3">
         <v>1300</v>
       </c>
       <c r="J24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1900</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1587,8 +1632,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1643,50 +1691,53 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E26" s="3">
         <v>3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I26" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J26" s="3">
         <v>3500</v>
       </c>
-      <c r="H26" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3100</v>
       </c>
-      <c r="J26" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6500</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,50 +1750,53 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E27" s="3">
         <v>3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I27" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J27" s="3">
         <v>3400</v>
       </c>
-      <c r="H27" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3000</v>
       </c>
-      <c r="J27" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6500</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1755,8 +1809,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1811,8 +1868,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1867,8 +1927,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1923,8 +1986,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1979,8 +2045,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1991,10 +2060,10 @@
         <v>-400</v>
       </c>
       <c r="F32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G32" s="3">
         <v>-300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-400</v>
       </c>
       <c r="H32" s="3">
         <v>-400</v>
@@ -2006,23 +2075,23 @@
         <v>-400</v>
       </c>
       <c r="K32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L32" s="3">
         <v>6900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5900</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2035,50 +2104,53 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E33" s="3">
         <v>3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I33" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J33" s="3">
         <v>3500</v>
       </c>
-      <c r="H33" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3100</v>
       </c>
-      <c r="J33" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6500</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2091,8 +2163,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2147,50 +2222,53 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E35" s="3">
         <v>3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I35" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J35" s="3">
         <v>3500</v>
       </c>
-      <c r="H35" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3100</v>
       </c>
-      <c r="J35" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6500</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2203,55 +2281,58 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
-        <v>45199</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
-        <v>45107</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2264,8 +2345,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2286,8 +2370,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2308,50 +2393,51 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>162900</v>
+      </c>
+      <c r="E41" s="3">
         <v>141200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>141100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>136500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
+        <v>177200</v>
+      </c>
+      <c r="I41" s="3">
+        <v>177200</v>
+      </c>
+      <c r="J41" s="3">
         <v>192600</v>
       </c>
-      <c r="H41" s="3">
-        <v>192600</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>211500</v>
       </c>
-      <c r="J41" s="3">
-        <v>211500</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7800</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2364,8 +2450,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2373,41 +2462,41 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>200</v>
       </c>
       <c r="G42" s="3">
+        <v>200</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>400</v>
       </c>
-      <c r="H42" s="3">
-        <v>400</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>100</v>
       </c>
-      <c r="J42" s="3">
-        <v>100</v>
-      </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>155000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>146300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>125900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>123800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>111200</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2420,8 +2509,11 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2446,8 +2538,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2476,8 +2568,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2502,8 +2597,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2532,35 +2627,38 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>12500</v>
+        <v>11800</v>
       </c>
       <c r="E45" s="3">
         <v>12500</v>
       </c>
       <c r="F45" s="3">
+        <v>12500</v>
+      </c>
+      <c r="G45" s="3">
         <v>12400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
+        <v>11900</v>
+      </c>
+      <c r="I45" s="3">
+        <v>11900</v>
+      </c>
+      <c r="J45" s="3">
         <v>10600</v>
       </c>
-      <c r="H45" s="3">
-        <v>10600</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>10200</v>
       </c>
-      <c r="J45" s="3">
-        <v>10200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2588,35 +2686,38 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>187100</v>
+      </c>
+      <c r="E46" s="3">
         <v>170500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>165500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>156700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
+        <v>198000</v>
+      </c>
+      <c r="I46" s="3">
+        <v>198000</v>
+      </c>
+      <c r="J46" s="3">
         <v>203700</v>
       </c>
-      <c r="H46" s="3">
-        <v>203700</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>221900</v>
       </c>
-      <c r="J46" s="3">
-        <v>221900</v>
-      </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2644,35 +2745,38 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E47" s="3">
         <v>110700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>112300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>105300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
+        <v>74100</v>
+      </c>
+      <c r="I47" s="3">
+        <v>74100</v>
+      </c>
+      <c r="J47" s="3">
         <v>25500</v>
       </c>
-      <c r="H47" s="3">
-        <v>25500</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>31000</v>
       </c>
-      <c r="J47" s="3">
-        <v>31000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2700,50 +2804,53 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E48" s="3">
         <v>25100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>25800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
+        <v>25600</v>
+      </c>
+      <c r="I48" s="3">
+        <v>25600</v>
+      </c>
+      <c r="J48" s="3">
         <v>26300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
+        <v>26900</v>
+      </c>
+      <c r="L48" s="3">
         <v>26300</v>
       </c>
-      <c r="I48" s="3">
-        <v>26900</v>
-      </c>
-      <c r="J48" s="3">
-        <v>26900</v>
-      </c>
-      <c r="K48" s="3">
-        <v>26300</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14900</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2756,37 +2863,40 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E49" s="3">
         <v>25200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>24900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>24600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
+        <v>24100</v>
+      </c>
+      <c r="I49" s="3">
+        <v>24100</v>
+      </c>
+      <c r="J49" s="3">
         <v>24000</v>
       </c>
-      <c r="H49" s="3">
-        <v>24000</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>23900</v>
       </c>
-      <c r="J49" s="3">
-        <v>23900</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19500</v>
-      </c>
-      <c r="L49" s="3">
-        <v>19600</v>
       </c>
       <c r="M49" s="3">
         <v>19600</v>
@@ -2797,8 +2907,8 @@
       <c r="O49" s="3">
         <v>19600</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>19600</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -2812,8 +2922,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2868,8 +2981,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2924,50 +3040,53 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E52" s="3">
         <v>11500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="J52" s="3">
         <v>8700</v>
       </c>
-      <c r="H52" s="3">
-        <v>8700</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>8100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>8100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>6000</v>
       </c>
       <c r="L52" s="3">
         <v>6000</v>
       </c>
       <c r="M52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N52" s="3">
         <v>6300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7300</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2980,8 +3099,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3036,50 +3158,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2312100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2327800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2331100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2307500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
+        <v>2270100</v>
+      </c>
+      <c r="I54" s="3">
+        <v>2270100</v>
+      </c>
+      <c r="J54" s="3">
         <v>2149500</v>
       </c>
-      <c r="H54" s="3">
-        <v>2149500</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2121800</v>
       </c>
-      <c r="J54" s="3">
-        <v>2121800</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1983700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1840100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1609800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1476700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1458200</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3092,8 +3217,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3114,8 +3242,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3136,50 +3265,51 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1954300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1957500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1941900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1917300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
+        <v>1904600</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1904600</v>
+      </c>
+      <c r="J57" s="3">
         <v>1735100</v>
       </c>
-      <c r="H57" s="3">
-        <v>1735100</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1593600</v>
       </c>
-      <c r="J57" s="3">
-        <v>1593600</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3192,34 +3322,37 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>900</v>
+      </c>
+      <c r="E58" s="3">
         <v>20700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>40900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>21200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>21200</v>
+      </c>
+      <c r="J58" s="3">
         <v>70000</v>
       </c>
-      <c r="H58" s="3">
-        <v>70000</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>160000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>160000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>24600</v>
       </c>
       <c r="L58" s="3">
         <v>24600</v>
@@ -3228,13 +3361,13 @@
         <v>24600</v>
       </c>
       <c r="N58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="O58" s="3">
         <v>24500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3">
+        <v>24500</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
@@ -3248,8 +3381,11 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3274,12 +3410,12 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>12100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3295,8 +3431,8 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
@@ -3304,35 +3440,38 @@
       <c r="T59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1956700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1980100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1984500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1938200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
+        <v>1927500</v>
+      </c>
+      <c r="I60" s="3">
+        <v>1927500</v>
+      </c>
+      <c r="J60" s="3">
         <v>1806900</v>
       </c>
-      <c r="H60" s="3">
-        <v>1806900</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1754900</v>
       </c>
-      <c r="J60" s="3">
-        <v>1754900</v>
-      </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3360,35 +3499,38 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>141500</v>
+      </c>
+      <c r="E61" s="3">
         <v>142000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>142600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>164800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>145200</v>
+      </c>
+      <c r="I61" s="3">
+        <v>145200</v>
+      </c>
+      <c r="J61" s="3">
         <v>145400</v>
       </c>
-      <c r="H61" s="3">
-        <v>145400</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>169800</v>
       </c>
-      <c r="J61" s="3">
-        <v>169800</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3416,35 +3558,38 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E62" s="3">
         <v>13500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
+        <v>12500</v>
+      </c>
+      <c r="I62" s="3">
+        <v>12500</v>
+      </c>
+      <c r="J62" s="3">
         <v>11400</v>
       </c>
-      <c r="H62" s="3">
-        <v>11400</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>14300</v>
       </c>
-      <c r="J62" s="3">
-        <v>14300</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -3472,8 +3617,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3528,8 +3676,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3584,8 +3735,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3640,50 +3794,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2115500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2135500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2141000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2118000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
+        <v>2085200</v>
+      </c>
+      <c r="I66" s="3">
+        <v>2085200</v>
+      </c>
+      <c r="J66" s="3">
         <v>1963600</v>
       </c>
-      <c r="H66" s="3">
-        <v>1963600</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1939000</v>
       </c>
-      <c r="J66" s="3">
-        <v>1939000</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1806100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1667500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1442400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1341900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1328800</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3696,8 +3853,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3718,8 +3878,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3774,8 +3935,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3830,8 +3994,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3842,7 +4009,7 @@
         <v>5000</v>
       </c>
       <c r="F70" s="3">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="G70" s="3">
         <v>3000</v>
@@ -3860,7 +4027,7 @@
         <v>3000</v>
       </c>
       <c r="L70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M70" s="3">
         <v>0</v>
@@ -3886,8 +4053,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3942,50 +4112,53 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E72" s="3">
         <v>64800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>62000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>61900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
+        <v>58600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>58600</v>
+      </c>
+      <c r="J72" s="3">
         <v>58700</v>
       </c>
-      <c r="H72" s="3">
-        <v>58700</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>55900</v>
       </c>
-      <c r="J72" s="3">
-        <v>55900</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>51100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>46500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>41400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>36800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>31500</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,8 +4171,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4054,8 +4230,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4110,8 +4289,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4166,50 +4348,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>191600</v>
+      </c>
+      <c r="E76" s="3">
         <v>187300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>185000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>186600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>181900</v>
+      </c>
+      <c r="I76" s="3">
+        <v>181900</v>
+      </c>
+      <c r="J76" s="3">
         <v>182900</v>
       </c>
-      <c r="H76" s="3">
-        <v>182900</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>179800</v>
       </c>
-      <c r="J76" s="3">
-        <v>179800</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>174700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>172600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>167400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>134800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>129400</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4222,8 +4407,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4278,55 +4466,58 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
-        <v>45199</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
-        <v>45107</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4339,50 +4530,53 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E81" s="3">
         <v>3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I81" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J81" s="3">
         <v>3500</v>
       </c>
-      <c r="H81" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3100</v>
       </c>
-      <c r="J81" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6500</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4395,8 +4589,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4417,31 +4614,32 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F83" s="3">
         <v>2100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H83" s="3">
         <v>900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3">
         <v>800</v>
-      </c>
-      <c r="H83" s="3">
-        <v>800</v>
-      </c>
-      <c r="I83" s="3">
-        <v>400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>400</v>
       </c>
       <c r="K83" s="3">
         <v>400</v>
@@ -4453,7 +4651,7 @@
         <v>400</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -4464,8 +4662,8 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
@@ -4473,8 +4671,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4529,8 +4730,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4585,8 +4789,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4641,8 +4848,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4697,8 +4907,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4753,44 +4966,47 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E89" s="3">
         <v>2400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J89" s="3">
         <v>900</v>
       </c>
-      <c r="H89" s="3">
-        <v>900</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>8000</v>
       </c>
-      <c r="J89" s="3">
-        <v>8000</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7500</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
@@ -4800,8 +5016,8 @@
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
@@ -4809,8 +5025,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4831,44 +5050,45 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1400</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-300</v>
       </c>
       <c r="G91" s="3">
         <v>-300</v>
       </c>
       <c r="H91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -4878,8 +5098,8 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -4887,8 +5107,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4943,8 +5166,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4999,44 +5225,47 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E94" s="3">
         <v>5900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-76200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-137400</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-137400</v>
+      </c>
+      <c r="J94" s="3">
         <v>-46600</v>
       </c>
-      <c r="H94" s="3">
-        <v>-46600</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-43400</v>
       </c>
-      <c r="J94" s="3">
-        <v>-43400</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-129400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-214700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-128300</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -5046,8 +5275,8 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5055,8 +5284,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5077,8 +5309,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5104,7 +5337,7 @@
         <v>700</v>
       </c>
       <c r="K96" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="L96" s="3">
         <v>-700</v>
@@ -5113,7 +5346,7 @@
         <v>-700</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -5133,8 +5366,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5189,8 +5425,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5245,8 +5484,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5301,44 +5543,47 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>24100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>31900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>117800</v>
+      </c>
+      <c r="I100" s="3">
+        <v>117800</v>
+      </c>
+      <c r="J100" s="3">
         <v>26800</v>
       </c>
-      <c r="H100" s="3">
-        <v>26800</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>42600</v>
       </c>
-      <c r="J100" s="3">
-        <v>42600</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>125600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>222900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>127700</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -5348,8 +5593,8 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
@@ -5357,8 +5602,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5383,8 +5631,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5413,44 +5661,47 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-40700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="J102" s="3">
         <v>-18900</v>
       </c>
-      <c r="H102" s="3">
-        <v>-18900</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>7200</v>
       </c>
-      <c r="J102" s="3">
-        <v>7200</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6800</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
@@ -5460,13 +5711,16 @@
       <c r="Q102" s="3">
         <v>0</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
   <si>
     <t>HNVR</t>
   </si>
@@ -656,81 +656,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
-      </c>
-      <c r="H7" s="2">
-        <v>45291</v>
       </c>
       <c r="I7" s="2">
         <v>45291</v>
       </c>
       <c r="J7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -743,53 +744,56 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E8" s="3">
         <v>17600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16200</v>
-      </c>
-      <c r="H8" s="3">
-        <v>15700</v>
       </c>
       <c r="I8" s="3">
         <v>15700</v>
       </c>
       <c r="J8" s="3">
-        <v>15000</v>
+        <v>15700</v>
       </c>
       <c r="K8" s="3">
         <v>15000</v>
       </c>
       <c r="L8" s="3">
+        <v>15000</v>
+      </c>
+      <c r="M8" s="3">
         <v>22600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16600</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -802,8 +806,11 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -861,37 +868,40 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E10" s="3">
         <v>17600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>16200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>15700</v>
       </c>
       <c r="I10" s="3">
         <v>15700</v>
       </c>
       <c r="J10" s="3">
-        <v>15000</v>
+        <v>15700</v>
       </c>
       <c r="K10" s="3">
         <v>15000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
+      <c r="L10" s="3">
+        <v>15000</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
@@ -920,8 +930,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -943,8 +956,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1002,8 +1016,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1061,8 +1078,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1078,20 +1098,20 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>-1000</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>-1000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>-1000</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1120,8 +1140,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1132,13 +1155,13 @@
         <v>500</v>
       </c>
       <c r="F15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G15" s="3">
         <v>600</v>
       </c>
       <c r="H15" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I15" s="3">
         <v>500</v>
@@ -1150,7 +1173,7 @@
         <v>500</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1179,8 +1202,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1199,53 +1225,54 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E17" s="3">
         <v>12000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>10300</v>
       </c>
       <c r="I17" s="3">
         <v>10300</v>
       </c>
       <c r="J17" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K17" s="3">
         <v>9900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2200</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1258,53 +1285,56 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E18" s="3">
         <v>5600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>5400</v>
       </c>
       <c r="I18" s="3">
         <v>5400</v>
       </c>
       <c r="J18" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K18" s="3">
         <v>5100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14400</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1317,8 +1347,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1340,13 +1373,14 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
         <v>400</v>
@@ -1355,10 +1389,10 @@
         <v>400</v>
       </c>
       <c r="G20" s="3">
+        <v>400</v>
+      </c>
+      <c r="H20" s="3">
         <v>300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>400</v>
       </c>
       <c r="I20" s="3">
         <v>400</v>
@@ -1370,23 +1404,23 @@
         <v>400</v>
       </c>
       <c r="L20" s="3">
+        <v>400</v>
+      </c>
+      <c r="M20" s="3">
         <v>-6900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1399,53 +1433,56 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E21" s="3">
         <v>5700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>5600</v>
       </c>
       <c r="I21" s="3">
         <v>5600</v>
       </c>
       <c r="J21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K21" s="3">
         <v>5200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1458,8 +1495,11 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1487,8 +1527,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1517,53 +1557,56 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E23" s="3">
         <v>5200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>5000</v>
       </c>
       <c r="I23" s="3">
         <v>5000</v>
       </c>
       <c r="J23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K23" s="3">
         <v>4700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8500</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1576,22 +1619,25 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1300</v>
       </c>
       <c r="H24" s="3">
         <v>1300</v>
@@ -1600,29 +1646,29 @@
         <v>1300</v>
       </c>
       <c r="J24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1900</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1635,8 +1681,11 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1694,53 +1743,56 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E26" s="3">
         <v>3900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>3800</v>
       </c>
       <c r="I26" s="3">
         <v>3800</v>
       </c>
       <c r="J26" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K26" s="3">
         <v>3500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6500</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1753,53 +1805,56 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E27" s="3">
         <v>3800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>4100</v>
       </c>
       <c r="I27" s="3">
         <v>4100</v>
       </c>
       <c r="J27" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K27" s="3">
         <v>3400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6500</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1812,8 +1867,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1871,8 +1929,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1930,8 +1991,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1989,8 +2053,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2048,13 +2115,16 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
         <v>-400</v>
@@ -2063,10 +2133,10 @@
         <v>-400</v>
       </c>
       <c r="G32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H32" s="3">
         <v>-300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-400</v>
       </c>
       <c r="I32" s="3">
         <v>-400</v>
@@ -2078,23 +2148,23 @@
         <v>-400</v>
       </c>
       <c r="L32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M32" s="3">
         <v>6900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5900</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2107,53 +2177,56 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E33" s="3">
         <v>3900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>3800</v>
       </c>
       <c r="I33" s="3">
         <v>3800</v>
       </c>
       <c r="J33" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K33" s="3">
         <v>3500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6500</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2166,8 +2239,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2225,53 +2301,56 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E35" s="3">
         <v>3900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>3800</v>
       </c>
       <c r="I35" s="3">
         <v>3800</v>
       </c>
       <c r="J35" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K35" s="3">
         <v>3500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6500</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,58 +2363,61 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
-      </c>
-      <c r="H38" s="2">
-        <v>45291</v>
       </c>
       <c r="I38" s="2">
         <v>45291</v>
       </c>
       <c r="J38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2348,8 +2430,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2371,8 +2456,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2394,53 +2480,54 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>160200</v>
+      </c>
+      <c r="E41" s="3">
         <v>162900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>141200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>141100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>136500</v>
-      </c>
-      <c r="H41" s="3">
-        <v>177200</v>
       </c>
       <c r="I41" s="3">
         <v>177200</v>
       </c>
       <c r="J41" s="3">
+        <v>177200</v>
+      </c>
+      <c r="K41" s="3">
         <v>192600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>211500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7800</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2453,8 +2540,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2465,41 +2555,41 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>200</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>155000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>146300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>125900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>123800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>111200</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2512,8 +2602,11 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2541,8 +2634,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2571,8 +2664,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2600,8 +2696,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2630,38 +2726,41 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>11800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>12500</v>
       </c>
       <c r="F45" s="3">
         <v>12500</v>
       </c>
       <c r="G45" s="3">
+        <v>12500</v>
+      </c>
+      <c r="H45" s="3">
         <v>12400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>11900</v>
       </c>
       <c r="I45" s="3">
         <v>11900</v>
       </c>
       <c r="J45" s="3">
+        <v>11900</v>
+      </c>
+      <c r="K45" s="3">
         <v>10600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10200</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2689,38 +2788,41 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>176500</v>
+      </c>
+      <c r="E46" s="3">
         <v>187100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>170500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>165500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>156700</v>
-      </c>
-      <c r="H46" s="3">
-        <v>198000</v>
       </c>
       <c r="I46" s="3">
         <v>198000</v>
       </c>
       <c r="J46" s="3">
+        <v>198000</v>
+      </c>
+      <c r="K46" s="3">
         <v>203700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>221900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2748,38 +2850,41 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>96900</v>
+      </c>
+      <c r="E47" s="3">
         <v>95400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>110700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>112300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>105300</v>
-      </c>
-      <c r="H47" s="3">
-        <v>74100</v>
       </c>
       <c r="I47" s="3">
         <v>74100</v>
       </c>
       <c r="J47" s="3">
+        <v>74100</v>
+      </c>
+      <c r="K47" s="3">
         <v>25500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>31000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2807,53 +2912,56 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E48" s="3">
         <v>23700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>25100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>25600</v>
       </c>
       <c r="I48" s="3">
         <v>25600</v>
       </c>
       <c r="J48" s="3">
+        <v>25600</v>
+      </c>
+      <c r="K48" s="3">
         <v>26300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>26900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2866,40 +2974,43 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E49" s="3">
         <v>25400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>25200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>24900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>24600</v>
-      </c>
-      <c r="H49" s="3">
-        <v>24100</v>
       </c>
       <c r="I49" s="3">
         <v>24100</v>
       </c>
       <c r="J49" s="3">
+        <v>24100</v>
+      </c>
+      <c r="K49" s="3">
         <v>24000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19500</v>
-      </c>
-      <c r="M49" s="3">
-        <v>19600</v>
       </c>
       <c r="N49" s="3">
         <v>19600</v>
@@ -2910,8 +3021,8 @@
       <c r="P49" s="3">
         <v>19600</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>19600</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -2925,8 +3036,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2984,8 +3098,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3043,22 +3160,25 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E52" s="3">
         <v>16200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>8200</v>
       </c>
       <c r="H52" s="3">
         <v>8200</v>
@@ -3067,29 +3187,29 @@
         <v>8200</v>
       </c>
       <c r="J52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K52" s="3">
         <v>8700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>6000</v>
       </c>
       <c r="M52" s="3">
         <v>6000</v>
       </c>
       <c r="N52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="O52" s="3">
         <v>6300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7300</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3102,8 +3222,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3161,53 +3284,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2291500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2312100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2327800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2331100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2307500</v>
-      </c>
-      <c r="H54" s="3">
-        <v>2270100</v>
       </c>
       <c r="I54" s="3">
         <v>2270100</v>
       </c>
       <c r="J54" s="3">
+        <v>2270100</v>
+      </c>
+      <c r="K54" s="3">
         <v>2149500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2121800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1983700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1840100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1609800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1476700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1458200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3220,8 +3346,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3243,8 +3372,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3266,53 +3396,54 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1936400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1954300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1957500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1941900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1917300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1904600</v>
       </c>
       <c r="I57" s="3">
         <v>1904600</v>
       </c>
       <c r="J57" s="3">
+        <v>1904600</v>
+      </c>
+      <c r="K57" s="3">
         <v>1735100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1593600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3325,37 +3456,40 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>20700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>40900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18900</v>
-      </c>
-      <c r="H58" s="3">
-        <v>21200</v>
       </c>
       <c r="I58" s="3">
         <v>21200</v>
       </c>
       <c r="J58" s="3">
+        <v>21200</v>
+      </c>
+      <c r="K58" s="3">
         <v>70000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>160000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>24600</v>
       </c>
       <c r="M58" s="3">
         <v>24600</v>
@@ -3364,13 +3498,13 @@
         <v>24600</v>
       </c>
       <c r="O58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="P58" s="3">
         <v>24500</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>24500</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
@@ -3384,8 +3518,11 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3413,12 +3550,12 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>12100</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3434,8 +3571,8 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
@@ -3443,38 +3580,41 @@
       <c r="U59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1936400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1956700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1980100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1984500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1938200</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1927500</v>
       </c>
       <c r="I60" s="3">
         <v>1927500</v>
       </c>
       <c r="J60" s="3">
+        <v>1927500</v>
+      </c>
+      <c r="K60" s="3">
         <v>1806900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1754900</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3502,38 +3642,41 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>141700</v>
+      </c>
+      <c r="E61" s="3">
         <v>141500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>142000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>142600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>164800</v>
-      </c>
-      <c r="H61" s="3">
-        <v>145200</v>
       </c>
       <c r="I61" s="3">
         <v>145200</v>
       </c>
       <c r="J61" s="3">
+        <v>145200</v>
+      </c>
+      <c r="K61" s="3">
         <v>145400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>169800</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3561,38 +3704,41 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E62" s="3">
         <v>17200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>12500</v>
       </c>
       <c r="I62" s="3">
         <v>12500</v>
       </c>
       <c r="J62" s="3">
+        <v>12500</v>
+      </c>
+      <c r="K62" s="3">
         <v>11400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14300</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3620,8 +3766,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3679,8 +3828,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3738,8 +3890,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3797,53 +3952,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2094900</v>
+      </c>
+      <c r="E66" s="3">
         <v>2115500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2135500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2141000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2118000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>2085200</v>
       </c>
       <c r="I66" s="3">
         <v>2085200</v>
       </c>
       <c r="J66" s="3">
+        <v>2085200</v>
+      </c>
+      <c r="K66" s="3">
         <v>1963600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1939000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1806100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1667500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1442400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1341900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1328800</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3856,8 +4014,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3879,8 +4040,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3938,8 +4100,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3997,13 +4162,16 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
         <v>5000</v>
@@ -4012,7 +4180,7 @@
         <v>5000</v>
       </c>
       <c r="G70" s="3">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H70" s="3">
         <v>3000</v>
@@ -4030,7 +4198,7 @@
         <v>3000</v>
       </c>
       <c r="M70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="N70" s="3">
         <v>0</v>
@@ -4056,8 +4224,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4115,53 +4286,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3">
         <v>67900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>64800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>62000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>61900</v>
-      </c>
-      <c r="H72" s="3">
-        <v>58600</v>
       </c>
       <c r="I72" s="3">
         <v>58600</v>
       </c>
       <c r="J72" s="3">
+        <v>58600</v>
+      </c>
+      <c r="K72" s="3">
         <v>58700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>55900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>51100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>46500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>41400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>36800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>31500</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4174,8 +4348,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4233,8 +4410,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4292,8 +4472,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4351,53 +4534,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>196600</v>
+      </c>
+      <c r="E76" s="3">
         <v>191600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>187300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>185000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>186600</v>
-      </c>
-      <c r="H76" s="3">
-        <v>181900</v>
       </c>
       <c r="I76" s="3">
         <v>181900</v>
       </c>
       <c r="J76" s="3">
+        <v>181900</v>
+      </c>
+      <c r="K76" s="3">
         <v>182900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>179800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>174700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>172600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>167400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>134800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>129400</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4410,8 +4596,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4469,58 +4658,61 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
-      </c>
-      <c r="H80" s="2">
-        <v>45291</v>
       </c>
       <c r="I80" s="2">
         <v>45291</v>
       </c>
       <c r="J80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4533,53 +4725,56 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E81" s="3">
         <v>3900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>3800</v>
       </c>
       <c r="I81" s="3">
         <v>3800</v>
       </c>
       <c r="J81" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K81" s="3">
         <v>3500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6500</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4592,8 +4787,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4615,8 +4813,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4627,22 +4826,22 @@
         <v>1000</v>
       </c>
       <c r="F83" s="3">
-        <v>2100</v>
+        <v>1000</v>
       </c>
       <c r="G83" s="3">
         <v>2100</v>
       </c>
       <c r="H83" s="3">
-        <v>900</v>
+        <v>2100</v>
       </c>
       <c r="I83" s="3">
         <v>900</v>
       </c>
       <c r="J83" s="3">
+        <v>900</v>
+      </c>
+      <c r="K83" s="3">
         <v>800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
@@ -4654,7 +4853,7 @@
         <v>400</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -4665,8 +4864,8 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -4674,8 +4873,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4733,8 +4935,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4792,8 +4997,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4851,8 +5059,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4910,8 +5121,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4969,47 +5183,50 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3600</v>
-      </c>
-      <c r="H89" s="3">
-        <v>4100</v>
       </c>
       <c r="I89" s="3">
         <v>4100</v>
       </c>
       <c r="J89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K89" s="3">
         <v>900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7500</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
         <v>0</v>
       </c>
@@ -5019,8 +5236,8 @@
       <c r="R89" s="3">
         <v>0</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
@@ -5028,8 +5245,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5051,47 +5271,48 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-400</v>
       </c>
       <c r="I91" s="3">
         <v>-400</v>
       </c>
       <c r="J91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -5101,8 +5322,8 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5110,8 +5331,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5169,8 +5393,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5228,47 +5455,50 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>42500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>5900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-76200</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-137400</v>
       </c>
       <c r="I94" s="3">
         <v>-137400</v>
       </c>
       <c r="J94" s="3">
+        <v>-137400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-46600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-43400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-129400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-214700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-128300</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -5278,8 +5508,8 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -5287,8 +5517,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5310,13 +5543,14 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>700</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E96" s="3">
         <v>700</v>
@@ -5340,7 +5574,7 @@
         <v>700</v>
       </c>
       <c r="L96" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="M96" s="3">
         <v>-700</v>
@@ -5349,7 +5583,7 @@
         <v>-700</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5369,8 +5603,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5428,8 +5665,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5487,8 +5727,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5546,47 +5789,50 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>24100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>31900</v>
-      </c>
-      <c r="H100" s="3">
-        <v>117800</v>
       </c>
       <c r="I100" s="3">
         <v>117800</v>
       </c>
       <c r="J100" s="3">
+        <v>117800</v>
+      </c>
+      <c r="K100" s="3">
         <v>26800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>42600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>125600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>222900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>127700</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -5596,8 +5842,8 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
@@ -5605,8 +5851,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5634,8 +5883,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5664,47 +5913,50 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>21600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-40700</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-15400</v>
       </c>
       <c r="I102" s="3">
         <v>-15400</v>
       </c>
       <c r="J102" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-18900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>16000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6800</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
@@ -5714,13 +5966,16 @@
       <c r="R102" s="3">
         <v>0</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>HNVR</t>
   </si>
@@ -656,85 +656,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45291</v>
       </c>
       <c r="J7" s="2">
         <v>45291</v>
       </c>
       <c r="K7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -747,56 +748,59 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E8" s="3">
         <v>17800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
+        <v>14700</v>
+      </c>
+      <c r="K8" s="3">
         <v>15700</v>
-      </c>
-      <c r="J8" s="3">
-        <v>15700</v>
-      </c>
-      <c r="K8" s="3">
-        <v>15000</v>
       </c>
       <c r="L8" s="3">
         <v>15000</v>
       </c>
       <c r="M8" s="3">
+        <v>15000</v>
+      </c>
+      <c r="N8" s="3">
         <v>22600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16600</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -809,8 +813,11 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -871,40 +878,43 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E10" s="3">
         <v>17800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>16900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>16200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
+        <v>14700</v>
+      </c>
+      <c r="K10" s="3">
         <v>15700</v>
-      </c>
-      <c r="J10" s="3">
-        <v>15700</v>
-      </c>
-      <c r="K10" s="3">
-        <v>15000</v>
       </c>
       <c r="L10" s="3">
         <v>15000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
+      <c r="M10" s="3">
+        <v>15000</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
@@ -933,8 +943,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,8 +970,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1019,8 +1033,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1081,8 +1098,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1101,20 +1121,20 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>-1000</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>-1000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3">
+        <v>-1000</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1143,8 +1163,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1158,13 +1181,13 @@
         <v>500</v>
       </c>
       <c r="G15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
         <v>600</v>
       </c>
       <c r="I15" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="J15" s="3">
         <v>500</v>
@@ -1176,7 +1199,7 @@
         <v>500</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1205,8 +1228,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1226,56 +1252,57 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E17" s="3">
         <v>15700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>10300</v>
       </c>
       <c r="J17" s="3">
         <v>10300</v>
       </c>
       <c r="K17" s="3">
+        <v>10300</v>
+      </c>
+      <c r="L17" s="3">
         <v>9900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2200</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1288,56 +1315,59 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E18" s="3">
         <v>2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K18" s="3">
         <v>5400</v>
       </c>
-      <c r="J18" s="3">
-        <v>5400</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14400</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,8 +1380,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1374,16 +1407,17 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
-      </c>
-      <c r="E20" s="3">
-        <v>400</v>
       </c>
       <c r="F20" s="3">
         <v>400</v>
@@ -1392,10 +1426,10 @@
         <v>400</v>
       </c>
       <c r="H20" s="3">
+        <v>400</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>400</v>
       </c>
       <c r="J20" s="3">
         <v>400</v>
@@ -1407,23 +1441,23 @@
         <v>400</v>
       </c>
       <c r="M20" s="3">
+        <v>400</v>
+      </c>
+      <c r="N20" s="3">
         <v>-6900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5900</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,56 +1470,59 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E21" s="3">
         <v>2300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K21" s="3">
         <v>5600</v>
       </c>
-      <c r="J21" s="3">
-        <v>5600</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,8 +1535,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1530,8 +1570,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1560,56 +1600,59 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>5000</v>
       </c>
       <c r="J23" s="3">
         <v>5000</v>
       </c>
       <c r="K23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L23" s="3">
         <v>4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8500</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1622,25 +1665,28 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1300</v>
       </c>
       <c r="I24" s="3">
         <v>1300</v>
@@ -1649,29 +1695,29 @@
         <v>1300</v>
       </c>
       <c r="K24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1900</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1684,8 +1730,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1746,56 +1795,59 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E26" s="3">
         <v>1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>3800</v>
       </c>
       <c r="J26" s="3">
         <v>3800</v>
       </c>
       <c r="K26" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L26" s="3">
         <v>3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6500</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,56 +1860,59 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E27" s="3">
         <v>1500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>4100</v>
       </c>
       <c r="J27" s="3">
         <v>4100</v>
       </c>
       <c r="K27" s="3">
+        <v>4100</v>
+      </c>
+      <c r="L27" s="3">
         <v>3400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6500</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1870,8 +1925,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1932,8 +1990,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1994,8 +2055,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2056,8 +2120,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2118,16 +2185,19 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-400</v>
       </c>
       <c r="F32" s="3">
         <v>-400</v>
@@ -2136,10 +2206,10 @@
         <v>-400</v>
       </c>
       <c r="H32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-400</v>
       </c>
       <c r="J32" s="3">
         <v>-400</v>
@@ -2151,23 +2221,23 @@
         <v>-400</v>
       </c>
       <c r="M32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N32" s="3">
         <v>6900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5900</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2180,56 +2250,59 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E33" s="3">
         <v>1500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>3800</v>
       </c>
       <c r="J33" s="3">
         <v>3800</v>
       </c>
       <c r="K33" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L33" s="3">
         <v>3500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6500</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2242,8 +2315,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2304,56 +2380,59 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E35" s="3">
         <v>1500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>3800</v>
       </c>
       <c r="J35" s="3">
         <v>3800</v>
       </c>
       <c r="K35" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L35" s="3">
         <v>3500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6500</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,61 +2445,64 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45291</v>
       </c>
       <c r="J38" s="2">
         <v>45291</v>
       </c>
       <c r="K38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2515,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2457,8 +2542,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2481,56 +2567,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>164500</v>
+      </c>
+      <c r="E41" s="3">
         <v>160200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>162900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>141200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>141100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>136500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>177200</v>
       </c>
       <c r="J41" s="3">
         <v>177200</v>
       </c>
       <c r="K41" s="3">
+        <v>177200</v>
+      </c>
+      <c r="L41" s="3">
         <v>192600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>211500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7800</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,8 +2630,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2558,41 +2648,41 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>200</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>155000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>146300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>125900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>123800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>111200</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2605,8 +2695,11 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2637,8 +2730,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2667,8 +2760,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2699,8 +2795,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2729,41 +2825,44 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>11700</v>
       </c>
       <c r="E45" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F45" s="3">
         <v>11800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>12500</v>
       </c>
       <c r="G45" s="3">
         <v>12500</v>
       </c>
       <c r="H45" s="3">
+        <v>12500</v>
+      </c>
+      <c r="I45" s="3">
         <v>12400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>11900</v>
       </c>
       <c r="J45" s="3">
         <v>11900</v>
       </c>
       <c r="K45" s="3">
+        <v>11900</v>
+      </c>
+      <c r="L45" s="3">
         <v>10600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10200</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -2791,41 +2890,44 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>176500</v>
+        <v>186800</v>
       </c>
       <c r="E46" s="3">
+        <v>188600</v>
+      </c>
+      <c r="F46" s="3">
         <v>187100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>170500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>165500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>156700</v>
-      </c>
-      <c r="I46" s="3">
-        <v>198000</v>
       </c>
       <c r="J46" s="3">
         <v>198000</v>
       </c>
       <c r="K46" s="3">
+        <v>198000</v>
+      </c>
+      <c r="L46" s="3">
         <v>203700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>221900</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -2853,41 +2955,44 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>96900</v>
+        <v>114100</v>
       </c>
       <c r="E47" s="3">
+        <v>104800</v>
+      </c>
+      <c r="F47" s="3">
         <v>95400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>110700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>112300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>105300</v>
-      </c>
-      <c r="I47" s="3">
-        <v>74100</v>
       </c>
       <c r="J47" s="3">
         <v>74100</v>
       </c>
       <c r="K47" s="3">
+        <v>74100</v>
+      </c>
+      <c r="L47" s="3">
         <v>25500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>31000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -2915,56 +3020,59 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E48" s="3">
         <v>23000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>25600</v>
       </c>
       <c r="J48" s="3">
         <v>25600</v>
       </c>
       <c r="K48" s="3">
+        <v>25600</v>
+      </c>
+      <c r="L48" s="3">
         <v>26300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>26300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,43 +3085,46 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>19200</v>
+        <v>25800</v>
       </c>
       <c r="E49" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F49" s="3">
         <v>25400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>25200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>24900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>24600</v>
-      </c>
-      <c r="I49" s="3">
-        <v>24100</v>
       </c>
       <c r="J49" s="3">
         <v>24100</v>
       </c>
       <c r="K49" s="3">
+        <v>24100</v>
+      </c>
+      <c r="L49" s="3">
         <v>24000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19500</v>
-      </c>
-      <c r="N49" s="3">
-        <v>19600</v>
       </c>
       <c r="O49" s="3">
         <v>19600</v>
@@ -3024,8 +3135,8 @@
       <c r="Q49" s="3">
         <v>19600</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3">
+        <v>19600</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -3039,8 +3150,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3101,8 +3215,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3163,25 +3280,28 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>38200</v>
+        <v>13600</v>
       </c>
       <c r="E52" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F52" s="3">
         <v>16200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>8200</v>
       </c>
       <c r="I52" s="3">
         <v>8200</v>
@@ -3190,29 +3310,29 @@
         <v>8200</v>
       </c>
       <c r="K52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="L52" s="3">
         <v>8700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>6000</v>
       </c>
       <c r="N52" s="3">
         <v>6000</v>
       </c>
       <c r="O52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="P52" s="3">
         <v>6300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7300</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3225,8 +3345,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3287,56 +3410,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2312000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2291500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2312100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2327800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2331100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2307500</v>
-      </c>
-      <c r="I54" s="3">
-        <v>2270100</v>
       </c>
       <c r="J54" s="3">
         <v>2270100</v>
       </c>
       <c r="K54" s="3">
+        <v>2270100</v>
+      </c>
+      <c r="L54" s="3">
         <v>2149500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2121800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1983700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1840100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1609800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1476700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1458200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3475,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3373,8 +3502,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3397,56 +3527,57 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1951300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1936400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1954300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1957500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1941900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1917300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1904600</v>
       </c>
       <c r="J57" s="3">
         <v>1904600</v>
       </c>
       <c r="K57" s="3">
+        <v>1904600</v>
+      </c>
+      <c r="L57" s="3">
         <v>1735100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1593600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3459,40 +3590,43 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="E58" s="3">
-        <v>900</v>
+        <v>8400</v>
       </c>
       <c r="F58" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G58" s="3">
         <v>20700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>40900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18900</v>
-      </c>
-      <c r="I58" s="3">
-        <v>21200</v>
       </c>
       <c r="J58" s="3">
         <v>21200</v>
       </c>
       <c r="K58" s="3">
+        <v>21200</v>
+      </c>
+      <c r="L58" s="3">
         <v>70000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>160000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>24600</v>
       </c>
       <c r="N58" s="3">
         <v>24600</v>
@@ -3501,13 +3635,13 @@
         <v>24600</v>
       </c>
       <c r="P58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="Q58" s="3">
         <v>24500</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>24500</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -3521,8 +3655,11 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3553,12 +3690,12 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>12100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3574,8 +3711,8 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
@@ -3583,41 +3720,44 @@
       <c r="V59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1936400</v>
+        <v>1961200</v>
       </c>
       <c r="E60" s="3">
-        <v>1956700</v>
+        <v>1946700</v>
       </c>
       <c r="F60" s="3">
+        <v>1963800</v>
+      </c>
+      <c r="G60" s="3">
         <v>1980100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1984500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1938200</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1927500</v>
       </c>
       <c r="J60" s="3">
         <v>1927500</v>
       </c>
       <c r="K60" s="3">
+        <v>1927500</v>
+      </c>
+      <c r="L60" s="3">
         <v>1806900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1754900</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3645,41 +3785,44 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>141700</v>
+        <v>137000</v>
       </c>
       <c r="E61" s="3">
-        <v>141500</v>
+        <v>134600</v>
       </c>
       <c r="F61" s="3">
+        <v>134400</v>
+      </c>
+      <c r="G61" s="3">
         <v>142000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>142600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>164800</v>
-      </c>
-      <c r="I61" s="3">
-        <v>145200</v>
       </c>
       <c r="J61" s="3">
         <v>145200</v>
       </c>
       <c r="K61" s="3">
+        <v>145200</v>
+      </c>
+      <c r="L61" s="3">
         <v>145400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>169800</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3707,41 +3850,44 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>16800</v>
+        <v>14900</v>
       </c>
       <c r="E62" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F62" s="3">
         <v>17200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>12500</v>
       </c>
       <c r="J62" s="3">
         <v>12500</v>
       </c>
       <c r="K62" s="3">
+        <v>12500</v>
+      </c>
+      <c r="L62" s="3">
         <v>11400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14300</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -3769,8 +3915,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3831,8 +3980,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3893,8 +4045,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3955,56 +4110,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2113100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2094900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2115500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2135500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2141000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2118000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>2085200</v>
       </c>
       <c r="J66" s="3">
         <v>2085200</v>
       </c>
       <c r="K66" s="3">
+        <v>2085200</v>
+      </c>
+      <c r="L66" s="3">
         <v>1963600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1939000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1806100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1667500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1442400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1341900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1328800</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4017,8 +4175,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4041,8 +4202,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4103,8 +4265,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4165,13 +4330,16 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="E70" s="3">
         <v>5000</v>
@@ -4183,7 +4351,7 @@
         <v>5000</v>
       </c>
       <c r="H70" s="3">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="I70" s="3">
         <v>3000</v>
@@ -4201,7 +4369,7 @@
         <v>3000</v>
       </c>
       <c r="N70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="O70" s="3">
         <v>0</v>
@@ -4227,8 +4395,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4289,56 +4460,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>70400</v>
       </c>
       <c r="E72" s="3">
+        <v>68700</v>
+      </c>
+      <c r="F72" s="3">
         <v>67900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>64800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>62000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>61900</v>
-      </c>
-      <c r="I72" s="3">
-        <v>58600</v>
       </c>
       <c r="J72" s="3">
         <v>58600</v>
       </c>
       <c r="K72" s="3">
+        <v>58600</v>
+      </c>
+      <c r="L72" s="3">
         <v>58700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>55900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>51100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>46500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>41400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>36800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>31500</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4351,8 +4525,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4413,8 +4590,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4475,8 +4655,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4537,56 +4720,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>196600</v>
+        <v>193800</v>
       </c>
       <c r="E76" s="3">
         <v>191600</v>
       </c>
       <c r="F76" s="3">
+        <v>191600</v>
+      </c>
+      <c r="G76" s="3">
         <v>187300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>185000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>186600</v>
-      </c>
-      <c r="I76" s="3">
-        <v>181900</v>
       </c>
       <c r="J76" s="3">
         <v>181900</v>
       </c>
       <c r="K76" s="3">
+        <v>181900</v>
+      </c>
+      <c r="L76" s="3">
         <v>182900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>179800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>174700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>172600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>167400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>134800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>129400</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4599,8 +4785,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4661,61 +4850,64 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45291</v>
       </c>
       <c r="J80" s="2">
         <v>45291</v>
       </c>
       <c r="K80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4728,56 +4920,59 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E81" s="3">
         <v>1500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>3800</v>
       </c>
       <c r="J81" s="3">
         <v>3800</v>
       </c>
       <c r="K81" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L81" s="3">
         <v>3500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6500</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4985,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4814,13 +5012,14 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="E83" s="3">
         <v>1000</v>
@@ -4841,10 +5040,10 @@
         <v>900</v>
       </c>
       <c r="K83" s="3">
+        <v>900</v>
+      </c>
+      <c r="L83" s="3">
         <v>800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>400</v>
       </c>
       <c r="M83" s="3">
         <v>400</v>
@@ -4856,7 +5055,7 @@
         <v>400</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4867,8 +5066,8 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -4876,8 +5075,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4938,8 +5140,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5000,8 +5205,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5062,8 +5270,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5124,8 +5335,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5186,50 +5400,53 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-2100</v>
       </c>
       <c r="E89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F89" s="3">
         <v>1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2400</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1400</v>
-      </c>
       <c r="H89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I89" s="3">
         <v>3600</v>
-      </c>
-      <c r="I89" s="3">
-        <v>4100</v>
       </c>
       <c r="J89" s="3">
         <v>4100</v>
       </c>
       <c r="K89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="L89" s="3">
         <v>900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7500</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
@@ -5239,8 +5456,8 @@
       <c r="S89" s="3">
         <v>0</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
@@ -5248,8 +5465,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5272,50 +5492,51 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3">
         <v>800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-400</v>
       </c>
       <c r="J91" s="3">
         <v>-400</v>
       </c>
       <c r="K91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -5325,8 +5546,8 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -5334,8 +5555,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5396,8 +5620,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5458,50 +5685,53 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-7700</v>
       </c>
       <c r="E94" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F94" s="3">
         <v>42500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>5900</v>
       </c>
-      <c r="G94" s="3">
-        <v>-18000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="I94" s="3">
         <v>-76200</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-137400</v>
       </c>
       <c r="J94" s="3">
         <v>-137400</v>
       </c>
       <c r="K94" s="3">
+        <v>-137400</v>
+      </c>
+      <c r="L94" s="3">
         <v>-46600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-43400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-129400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-214700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-128300</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -5511,8 +5741,8 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -5520,8 +5750,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5544,13 +5777,14 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>3</v>
+      <c r="D96" s="3">
+        <v>800</v>
       </c>
       <c r="E96" s="3">
         <v>700</v>
@@ -5577,7 +5811,7 @@
         <v>700</v>
       </c>
       <c r="M96" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="N96" s="3">
         <v>-700</v>
@@ -5586,7 +5820,7 @@
         <v>-700</v>
       </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5606,8 +5840,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5668,8 +5905,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5730,8 +5970,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,50 +6035,53 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>14100</v>
       </c>
       <c r="E100" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-22200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>24100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>31900</v>
-      </c>
-      <c r="I100" s="3">
-        <v>117800</v>
       </c>
       <c r="J100" s="3">
         <v>117800</v>
       </c>
       <c r="K100" s="3">
+        <v>117800</v>
+      </c>
+      <c r="L100" s="3">
         <v>26800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>42600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>125600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>222900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>127700</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
@@ -5845,8 +6091,8 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
@@ -5854,8 +6100,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5886,8 +6135,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5916,50 +6165,53 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="E102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F102" s="3">
         <v>21600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-40700</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-15400</v>
       </c>
       <c r="J102" s="3">
         <v>-15400</v>
       </c>
       <c r="K102" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="L102" s="3">
         <v>-18900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>16000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6800</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
@@ -5969,13 +6221,16 @@
       <c r="S102" s="3">
         <v>0</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
   <si>
     <t>HNVR</t>
   </si>
@@ -656,93 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
-      </c>
-      <c r="K7" s="2">
-        <v>45291</v>
       </c>
       <c r="L7" s="2">
         <v>45291</v>
       </c>
       <c r="M7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -755,62 +755,65 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E8" s="3">
         <v>16700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15700</v>
-      </c>
-      <c r="M8" s="3">
-        <v>15000</v>
       </c>
       <c r="N8" s="3">
         <v>15000</v>
       </c>
       <c r="O8" s="3">
+        <v>15000</v>
+      </c>
+      <c r="P8" s="3">
         <v>22600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16600</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -823,8 +826,11 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -891,46 +897,49 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E10" s="3">
         <v>16700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>17800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>17600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>16900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>16200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15700</v>
-      </c>
-      <c r="M10" s="3">
-        <v>15000</v>
       </c>
       <c r="N10" s="3">
         <v>15000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
+      <c r="O10" s="3">
+        <v>15000</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
@@ -959,8 +968,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,8 +997,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1053,8 +1066,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,13 +1137,16 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>3200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1147,20 +1166,20 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>-1000</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>-1000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>-1000</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1189,8 +1208,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1210,13 +1232,13 @@
         <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J15" s="3">
         <v>600</v>
       </c>
       <c r="K15" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="L15" s="3">
         <v>500</v>
@@ -1228,7 +1250,7 @@
         <v>500</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1257,8 +1279,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,62 +1305,63 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E17" s="3">
         <v>11700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10500</v>
-      </c>
-      <c r="K17" s="3">
-        <v>10300</v>
       </c>
       <c r="L17" s="3">
         <v>10300</v>
       </c>
       <c r="M17" s="3">
+        <v>10300</v>
+      </c>
+      <c r="N17" s="3">
         <v>9900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2200</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,62 +1374,65 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E18" s="3">
         <v>5000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>14200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>14400</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1445,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,22 +1474,23 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>400</v>
       </c>
       <c r="H20" s="3">
         <v>400</v>
@@ -1466,10 +1499,10 @@
         <v>400</v>
       </c>
       <c r="J20" s="3">
+        <v>400</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>400</v>
       </c>
       <c r="L20" s="3">
         <v>400</v>
@@ -1481,23 +1514,23 @@
         <v>400</v>
       </c>
       <c r="O20" s="3">
+        <v>400</v>
+      </c>
+      <c r="P20" s="3">
         <v>-6900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5900</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1510,62 +1543,65 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E21" s="3">
         <v>5200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,8 +1614,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1616,8 +1655,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1646,62 +1685,65 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="E23" s="3">
         <v>4700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5400</v>
-      </c>
-      <c r="K23" s="3">
-        <v>5000</v>
       </c>
       <c r="L23" s="3">
         <v>5000</v>
       </c>
       <c r="M23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N23" s="3">
         <v>4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8500</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,31 +1756,34 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>1300</v>
       </c>
       <c r="K24" s="3">
         <v>1300</v>
@@ -1747,29 +1792,29 @@
         <v>1300</v>
       </c>
       <c r="M24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N24" s="3">
         <v>1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1900</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1782,8 +1827,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,62 +1898,65 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4100</v>
-      </c>
-      <c r="K26" s="3">
-        <v>3800</v>
       </c>
       <c r="L26" s="3">
         <v>3800</v>
       </c>
       <c r="M26" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N26" s="3">
         <v>3500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6500</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,62 +1969,65 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>4100</v>
       </c>
       <c r="L27" s="3">
         <v>4100</v>
       </c>
       <c r="M27" s="3">
+        <v>4100</v>
+      </c>
+      <c r="N27" s="3">
         <v>3400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6500</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1986,8 +2040,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,8 +2111,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2122,8 +2182,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2253,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,22 +2324,25 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-400</v>
       </c>
       <c r="H32" s="3">
         <v>-400</v>
@@ -2282,10 +2351,10 @@
         <v>-400</v>
       </c>
       <c r="J32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-400</v>
       </c>
       <c r="L32" s="3">
         <v>-400</v>
@@ -2297,23 +2366,23 @@
         <v>-400</v>
       </c>
       <c r="O32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P32" s="3">
         <v>6900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5900</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2326,62 +2395,65 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4100</v>
-      </c>
-      <c r="K33" s="3">
-        <v>3800</v>
       </c>
       <c r="L33" s="3">
         <v>3800</v>
       </c>
       <c r="M33" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N33" s="3">
         <v>3500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6500</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2394,8 +2466,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,62 +2537,65 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4100</v>
-      </c>
-      <c r="K35" s="3">
-        <v>3800</v>
       </c>
       <c r="L35" s="3">
         <v>3800</v>
       </c>
       <c r="M35" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N35" s="3">
         <v>3500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6500</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2530,67 +2608,70 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
-      </c>
-      <c r="K38" s="2">
-        <v>45291</v>
       </c>
       <c r="L38" s="2">
         <v>45291</v>
       </c>
       <c r="M38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2603,8 +2684,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2713,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,62 +2740,63 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>208900</v>
+      </c>
+      <c r="E41" s="3">
         <v>167600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>164500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>160200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>162900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>141200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>141100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>136500</v>
-      </c>
-      <c r="K41" s="3">
-        <v>177200</v>
       </c>
       <c r="L41" s="3">
         <v>177200</v>
       </c>
       <c r="M41" s="3">
+        <v>177200</v>
+      </c>
+      <c r="N41" s="3">
         <v>192600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>211500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7800</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2723,8 +2809,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2741,44 +2830,44 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>200</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>155000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>146300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>125900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>123800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>111200</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,8 +2880,11 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2829,8 +2921,8 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2859,13 +2951,16 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>700</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>3</v>
@@ -2897,8 +2992,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2927,8 +3022,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2936,38 +3034,38 @@
         <v>11800</v>
       </c>
       <c r="E45" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F45" s="3">
         <v>11700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>12500</v>
       </c>
       <c r="I45" s="3">
         <v>12500</v>
       </c>
       <c r="J45" s="3">
+        <v>12500</v>
+      </c>
+      <c r="K45" s="3">
         <v>12400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>11900</v>
       </c>
       <c r="L45" s="3">
         <v>11900</v>
       </c>
       <c r="M45" s="3">
+        <v>11900</v>
+      </c>
+      <c r="N45" s="3">
         <v>10600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10200</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -2995,47 +3093,50 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>227700</v>
+      </c>
+      <c r="E46" s="3">
         <v>188200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>186800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>188600</v>
       </c>
-      <c r="G46" s="3">
-        <v>187100</v>
-      </c>
       <c r="H46" s="3">
+        <v>188700</v>
+      </c>
+      <c r="I46" s="3">
         <v>170500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>165500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>156700</v>
-      </c>
-      <c r="K46" s="3">
-        <v>198000</v>
       </c>
       <c r="L46" s="3">
         <v>198000</v>
       </c>
       <c r="M46" s="3">
+        <v>198000</v>
+      </c>
+      <c r="N46" s="3">
         <v>203700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>221900</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3063,47 +3164,50 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>108400</v>
+      </c>
+      <c r="E47" s="3">
         <v>111100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>114100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>104800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>95400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>110700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>112300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>105300</v>
-      </c>
-      <c r="K47" s="3">
-        <v>74100</v>
       </c>
       <c r="L47" s="3">
         <v>74100</v>
       </c>
       <c r="M47" s="3">
+        <v>74100</v>
+      </c>
+      <c r="N47" s="3">
         <v>25500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>31000</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -3131,62 +3235,65 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E48" s="3">
         <v>24900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>25300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>25600</v>
       </c>
       <c r="L48" s="3">
         <v>25600</v>
       </c>
       <c r="M48" s="3">
+        <v>25600</v>
+      </c>
+      <c r="N48" s="3">
         <v>26300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,49 +3306,52 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>25800</v>
+        <v>25500</v>
       </c>
       <c r="E49" s="3">
         <v>25800</v>
       </c>
       <c r="F49" s="3">
+        <v>25800</v>
+      </c>
+      <c r="G49" s="3">
         <v>25600</v>
-      </c>
-      <c r="G49" s="3">
-        <v>25400</v>
       </c>
       <c r="H49" s="3">
         <v>25200</v>
       </c>
       <c r="I49" s="3">
+        <v>25200</v>
+      </c>
+      <c r="J49" s="3">
         <v>24900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>24600</v>
-      </c>
-      <c r="K49" s="3">
-        <v>24100</v>
       </c>
       <c r="L49" s="3">
         <v>24100</v>
       </c>
       <c r="M49" s="3">
+        <v>24100</v>
+      </c>
+      <c r="N49" s="3">
         <v>24000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19500</v>
-      </c>
-      <c r="P49" s="3">
-        <v>19600</v>
       </c>
       <c r="Q49" s="3">
         <v>19600</v>
@@ -3252,8 +3362,8 @@
       <c r="S49" s="3">
         <v>19600</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
+      <c r="T49" s="3">
+        <v>19600</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
@@ -3267,8 +3377,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3448,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,31 +3519,34 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E52" s="3">
         <v>13700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10300</v>
       </c>
-      <c r="G52" s="3">
-        <v>16200</v>
-      </c>
       <c r="H52" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I52" s="3">
         <v>11500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>8200</v>
       </c>
       <c r="K52" s="3">
         <v>8200</v>
@@ -3436,29 +3555,29 @@
         <v>8200</v>
       </c>
       <c r="M52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="N52" s="3">
         <v>8700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>6000</v>
       </c>
       <c r="P52" s="3">
         <v>6000</v>
       </c>
       <c r="Q52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="R52" s="3">
         <v>6300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7300</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3590,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,62 +3661,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2383100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2331600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2312000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2291500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2312100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2327800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2331100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2307500</v>
-      </c>
-      <c r="K54" s="3">
-        <v>2270100</v>
       </c>
       <c r="L54" s="3">
         <v>2270100</v>
       </c>
       <c r="M54" s="3">
+        <v>2270100</v>
+      </c>
+      <c r="N54" s="3">
         <v>2149500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2121800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1983700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1840100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1609800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1476700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1458200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3732,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3761,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,62 +3788,63 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2028400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1974800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1951300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1936400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1954300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1957500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1941900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1917300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1904600</v>
       </c>
       <c r="L57" s="3">
         <v>1904600</v>
       </c>
       <c r="M57" s="3">
+        <v>1904600</v>
+      </c>
+      <c r="N57" s="3">
         <v>1735100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1593600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,46 +3857,49 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1200</v>
-      </c>
-      <c r="E58" s="3">
-        <v>8400</v>
       </c>
       <c r="F58" s="3">
         <v>8400</v>
       </c>
       <c r="G58" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H58" s="3">
         <v>8000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>40900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>18900</v>
-      </c>
-      <c r="K58" s="3">
-        <v>21200</v>
       </c>
       <c r="L58" s="3">
         <v>21200</v>
       </c>
       <c r="M58" s="3">
+        <v>21200</v>
+      </c>
+      <c r="N58" s="3">
         <v>70000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>160000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>24600</v>
       </c>
       <c r="P58" s="3">
         <v>24600</v>
@@ -3775,13 +3908,13 @@
         <v>24600</v>
       </c>
       <c r="R58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="S58" s="3">
         <v>24500</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>24500</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -3795,8 +3928,11 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3833,12 +3969,12 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>12100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3854,8 +3990,8 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -3863,47 +3999,50 @@
       <c r="X59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2074200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1977800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1961200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1946700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1963800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1980100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1984500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1938200</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1927500</v>
       </c>
       <c r="L60" s="3">
         <v>1927500</v>
       </c>
       <c r="M60" s="3">
+        <v>1927500</v>
+      </c>
+      <c r="N60" s="3">
         <v>1806900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1754900</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -3931,47 +4070,50 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E61" s="3">
         <v>136500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>137000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>134600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>134400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>142000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>142600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>164800</v>
-      </c>
-      <c r="K61" s="3">
-        <v>145200</v>
       </c>
       <c r="L61" s="3">
         <v>145200</v>
       </c>
       <c r="M61" s="3">
+        <v>145200</v>
+      </c>
+      <c r="N61" s="3">
         <v>145400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>169800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3999,47 +4141,50 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E62" s="3">
         <v>15400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>12500</v>
       </c>
       <c r="L62" s="3">
         <v>12500</v>
       </c>
       <c r="M62" s="3">
+        <v>12500</v>
+      </c>
+      <c r="N62" s="3">
         <v>11400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14300</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -4067,8 +4212,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4283,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4354,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,62 +4425,65 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2182800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2129700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2113100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2094900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2115500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2135500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2141000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2118000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>2085200</v>
       </c>
       <c r="L66" s="3">
         <v>2085200</v>
       </c>
       <c r="M66" s="3">
+        <v>2085200</v>
+      </c>
+      <c r="N66" s="3">
         <v>1963600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1939000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1806100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1667500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1442400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1341900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1328800</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4339,8 +4496,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4525,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4594,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4665,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4525,7 +4692,7 @@
         <v>5000</v>
       </c>
       <c r="J70" s="3">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="K70" s="3">
         <v>3000</v>
@@ -4543,7 +4710,7 @@
         <v>3000</v>
       </c>
       <c r="P70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
@@ -4569,8 +4736,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,62 +4807,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E72" s="3">
         <v>73100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>70400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>68700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>67900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>64800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>62000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>61900</v>
-      </c>
-      <c r="K72" s="3">
-        <v>58600</v>
       </c>
       <c r="L72" s="3">
         <v>58600</v>
       </c>
       <c r="M72" s="3">
+        <v>58600</v>
+      </c>
+      <c r="N72" s="3">
         <v>58700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>55900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>51100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>46500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>41400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>36800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>31500</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,8 +4878,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +4949,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5020,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,62 +5091,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>195200</v>
+      </c>
+      <c r="E76" s="3">
         <v>196800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>193800</v>
-      </c>
-      <c r="F76" s="3">
-        <v>191600</v>
       </c>
       <c r="G76" s="3">
         <v>191600</v>
       </c>
       <c r="H76" s="3">
+        <v>191600</v>
+      </c>
+      <c r="I76" s="3">
         <v>187300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>185000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>186600</v>
-      </c>
-      <c r="K76" s="3">
-        <v>181900</v>
       </c>
       <c r="L76" s="3">
         <v>181900</v>
       </c>
       <c r="M76" s="3">
+        <v>181900</v>
+      </c>
+      <c r="N76" s="3">
         <v>182900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>179800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>174700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>172600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>167400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>134800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>129400</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4977,8 +5162,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,67 +5233,70 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
-      </c>
-      <c r="K80" s="2">
-        <v>45291</v>
       </c>
       <c r="L80" s="2">
         <v>45291</v>
       </c>
       <c r="M80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5118,62 +5309,65 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4100</v>
-      </c>
-      <c r="K81" s="3">
-        <v>3800</v>
       </c>
       <c r="L81" s="3">
         <v>3800</v>
       </c>
       <c r="M81" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N81" s="3">
         <v>3500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6500</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5186,8 +5380,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,31 +5409,32 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1000</v>
       </c>
       <c r="G83" s="3">
         <v>1000</v>
       </c>
       <c r="H83" s="3">
-        <v>2100</v>
+        <v>1000</v>
       </c>
       <c r="I83" s="3">
         <v>2100</v>
       </c>
       <c r="J83" s="3">
-        <v>900</v>
+        <v>2100</v>
       </c>
       <c r="K83" s="3">
         <v>900</v>
@@ -5245,10 +5443,10 @@
         <v>900</v>
       </c>
       <c r="M83" s="3">
+        <v>900</v>
+      </c>
+      <c r="N83" s="3">
         <v>800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>400</v>
       </c>
       <c r="O83" s="3">
         <v>400</v>
@@ -5260,7 +5458,7 @@
         <v>400</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -5271,8 +5469,8 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5280,8 +5478,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5549,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5620,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5691,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5762,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,56 +5833,59 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E89" s="3">
         <v>2700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4100</v>
       </c>
-      <c r="G89" s="3">
-        <v>1300</v>
-      </c>
       <c r="H89" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3600</v>
-      </c>
-      <c r="K89" s="3">
-        <v>4100</v>
       </c>
       <c r="L89" s="3">
         <v>4100</v>
       </c>
       <c r="M89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="N89" s="3">
         <v>900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7500</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
@@ -5679,8 +5895,8 @@
       <c r="U89" s="3">
         <v>0</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
@@ -5688,8 +5904,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,56 +5933,57 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-400</v>
       </c>
       <c r="L91" s="3">
         <v>-400</v>
       </c>
       <c r="M91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -5773,8 +5993,8 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -5782,8 +6002,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6073,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,56 +6144,59 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>13000</v>
       </c>
-      <c r="G94" s="3">
-        <v>42500</v>
-      </c>
       <c r="H94" s="3">
+        <v>38300</v>
+      </c>
+      <c r="I94" s="3">
         <v>8800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-76200</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-137400</v>
       </c>
       <c r="L94" s="3">
         <v>-137400</v>
       </c>
       <c r="M94" s="3">
+        <v>-137400</v>
+      </c>
+      <c r="N94" s="3">
         <v>-46600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-43400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-129400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-214700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-128300</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -5977,8 +6206,8 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -5986,8 +6215,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,19 +6244,20 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>800</v>
+      </c>
+      <c r="E96" s="3">
         <v>700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>800</v>
-      </c>
-      <c r="F96" s="3">
-        <v>700</v>
       </c>
       <c r="G96" s="3">
         <v>700</v>
@@ -6051,7 +6284,7 @@
         <v>700</v>
       </c>
       <c r="O96" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="P96" s="3">
         <v>-700</v>
@@ -6060,7 +6293,7 @@
         <v>-700</v>
       </c>
       <c r="R96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -6080,8 +6313,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6384,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6455,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,56 +6526,59 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E100" s="3">
         <v>15200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>14100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-19800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-22200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>24100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>31900</v>
-      </c>
-      <c r="K100" s="3">
-        <v>117800</v>
       </c>
       <c r="L100" s="3">
         <v>117800</v>
       </c>
       <c r="M100" s="3">
+        <v>117800</v>
+      </c>
+      <c r="N100" s="3">
         <v>26800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>42600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>125600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>222900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>127700</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -6343,8 +6588,8 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
@@ -6352,8 +6597,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6390,8 +6638,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6420,56 +6668,59 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E102" s="3">
         <v>3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>21600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-40700</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-15400</v>
       </c>
       <c r="L102" s="3">
         <v>-15400</v>
       </c>
       <c r="M102" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="N102" s="3">
         <v>-18900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>16000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6800</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
@@ -6479,13 +6730,16 @@
       <c r="U102" s="3">
         <v>0</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HNVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
   <si>
     <t>HNVR</t>
   </si>
@@ -656,96 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
-      </c>
-      <c r="L7" s="2">
-        <v>45291</v>
       </c>
       <c r="M7" s="2">
         <v>45291</v>
       </c>
       <c r="N7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -758,65 +759,68 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E8" s="3">
         <v>12500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15700</v>
-      </c>
-      <c r="N8" s="3">
-        <v>15000</v>
       </c>
       <c r="O8" s="3">
         <v>15000</v>
       </c>
       <c r="P8" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Q8" s="3">
         <v>22600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16600</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -829,8 +833,11 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -900,49 +907,52 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E10" s="3">
         <v>12500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>16000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>17800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>17600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>16200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15700</v>
-      </c>
-      <c r="N10" s="3">
-        <v>15000</v>
       </c>
       <c r="O10" s="3">
         <v>15000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
+      <c r="P10" s="3">
+        <v>15000</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
@@ -971,8 +981,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -998,8 +1011,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1069,8 +1083,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1140,17 +1157,20 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E14" s="3">
         <v>3200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1169,20 +1189,20 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>-1000</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>-1000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>-1000</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1211,8 +1231,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1235,13 +1258,13 @@
         <v>500</v>
       </c>
       <c r="J15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>600</v>
       </c>
       <c r="L15" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M15" s="3">
         <v>500</v>
@@ -1253,7 +1276,7 @@
         <v>500</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1282,8 +1305,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1306,65 +1332,66 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10500</v>
-      </c>
-      <c r="L17" s="3">
-        <v>10300</v>
       </c>
       <c r="M17" s="3">
         <v>10300</v>
       </c>
       <c r="N17" s="3">
+        <v>10300</v>
+      </c>
+      <c r="O17" s="3">
         <v>9900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2200</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1377,65 +1404,68 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E18" s="3">
         <v>3700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>14200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>14400</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1448,8 +1478,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1475,8 +1508,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1484,16 +1518,16 @@
         <v>400</v>
       </c>
       <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>400</v>
       </c>
       <c r="I20" s="3">
         <v>400</v>
@@ -1502,10 +1536,10 @@
         <v>400</v>
       </c>
       <c r="K20" s="3">
+        <v>400</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>400</v>
       </c>
       <c r="M20" s="3">
         <v>400</v>
@@ -1517,23 +1551,23 @@
         <v>400</v>
       </c>
       <c r="P20" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5900</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1546,65 +1580,68 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E21" s="3">
         <v>3900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1617,8 +1654,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1658,8 +1698,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1688,65 +1728,68 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5400</v>
-      </c>
-      <c r="L23" s="3">
-        <v>5000</v>
       </c>
       <c r="M23" s="3">
         <v>5000</v>
       </c>
       <c r="N23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O23" s="3">
         <v>4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8500</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1759,34 +1802,37 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
-      </c>
-      <c r="K24" s="3">
-        <v>1300</v>
       </c>
       <c r="L24" s="3">
         <v>1300</v>
@@ -1795,29 +1841,29 @@
         <v>1300</v>
       </c>
       <c r="N24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1900</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1830,8 +1876,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1901,65 +1950,68 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4100</v>
-      </c>
-      <c r="L26" s="3">
-        <v>3800</v>
       </c>
       <c r="M26" s="3">
         <v>3800</v>
       </c>
       <c r="N26" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O26" s="3">
         <v>3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6500</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1972,65 +2024,68 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>3400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3900</v>
-      </c>
-      <c r="L27" s="3">
-        <v>4100</v>
       </c>
       <c r="M27" s="3">
         <v>4100</v>
       </c>
       <c r="N27" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O27" s="3">
         <v>3400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6500</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2043,8 +2098,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2114,8 +2172,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2185,8 +2246,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2256,8 +2320,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2327,8 +2394,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2336,16 +2406,16 @@
         <v>-400</v>
       </c>
       <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-400</v>
       </c>
       <c r="I32" s="3">
         <v>-400</v>
@@ -2354,10 +2424,10 @@
         <v>-400</v>
       </c>
       <c r="K32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-400</v>
       </c>
       <c r="M32" s="3">
         <v>-400</v>
@@ -2369,23 +2439,23 @@
         <v>-400</v>
       </c>
       <c r="P32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q32" s="3">
         <v>6900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5900</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2398,65 +2468,68 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4100</v>
-      </c>
-      <c r="L33" s="3">
-        <v>3800</v>
       </c>
       <c r="M33" s="3">
         <v>3800</v>
       </c>
       <c r="N33" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O33" s="3">
         <v>3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6500</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,8 +2542,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2540,65 +2616,68 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4100</v>
-      </c>
-      <c r="L35" s="3">
-        <v>3800</v>
       </c>
       <c r="M35" s="3">
         <v>3800</v>
       </c>
       <c r="N35" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O35" s="3">
         <v>3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6500</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2611,70 +2690,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
-      </c>
-      <c r="L38" s="2">
-        <v>45291</v>
       </c>
       <c r="M38" s="2">
         <v>45291</v>
       </c>
       <c r="N38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2687,8 +2769,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2714,8 +2799,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2741,65 +2827,66 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>194400</v>
+      </c>
+      <c r="E41" s="3">
         <v>208900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>167600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>164500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>160200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>162900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>141200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>141100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>136500</v>
-      </c>
-      <c r="L41" s="3">
-        <v>177200</v>
       </c>
       <c r="M41" s="3">
         <v>177200</v>
       </c>
       <c r="N41" s="3">
+        <v>177200</v>
+      </c>
+      <c r="O41" s="3">
         <v>192600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>211500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7800</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2812,8 +2899,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2830,47 +2920,47 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>1600</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>200</v>
       </c>
       <c r="L42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>155000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>146300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>125900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>123800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>111200</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2883,13 +2973,16 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>700</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -2924,8 +3017,8 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2954,17 +3047,20 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3">
         <v>700</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,8 +3091,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3025,50 +3121,53 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>11800</v>
+        <v>11500</v>
       </c>
       <c r="E45" s="3">
         <v>11800</v>
       </c>
       <c r="F45" s="3">
+        <v>11800</v>
+      </c>
+      <c r="G45" s="3">
         <v>11700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>12500</v>
       </c>
       <c r="J45" s="3">
         <v>12500</v>
       </c>
       <c r="K45" s="3">
+        <v>12500</v>
+      </c>
+      <c r="L45" s="3">
         <v>12400</v>
-      </c>
-      <c r="L45" s="3">
-        <v>11900</v>
       </c>
       <c r="M45" s="3">
         <v>11900</v>
       </c>
       <c r="N45" s="3">
+        <v>11900</v>
+      </c>
+      <c r="O45" s="3">
         <v>10600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10200</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -3096,50 +3195,53 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>222900</v>
+      </c>
+      <c r="E46" s="3">
         <v>227700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>188200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>186800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>188600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>188700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>170500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>165500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>156700</v>
-      </c>
-      <c r="L46" s="3">
-        <v>198000</v>
       </c>
       <c r="M46" s="3">
         <v>198000</v>
       </c>
       <c r="N46" s="3">
+        <v>198000</v>
+      </c>
+      <c r="O46" s="3">
         <v>203700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>221900</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3167,50 +3269,53 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>112700</v>
+      </c>
+      <c r="E47" s="3">
         <v>108400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>111100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>114100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>104800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>95400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>110700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>112300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>105300</v>
-      </c>
-      <c r="L47" s="3">
-        <v>74100</v>
       </c>
       <c r="M47" s="3">
         <v>74100</v>
       </c>
       <c r="N47" s="3">
+        <v>74100</v>
+      </c>
+      <c r="O47" s="3">
         <v>25500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>31000</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -3238,65 +3343,68 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E48" s="3">
         <v>24200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>25600</v>
       </c>
       <c r="M48" s="3">
         <v>25600</v>
       </c>
       <c r="N48" s="3">
+        <v>25600</v>
+      </c>
+      <c r="O48" s="3">
         <v>26300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>14900</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3309,52 +3417,55 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E49" s="3">
         <v>25500</v>
-      </c>
-      <c r="E49" s="3">
-        <v>25800</v>
       </c>
       <c r="F49" s="3">
         <v>25800</v>
       </c>
       <c r="G49" s="3">
+        <v>25800</v>
+      </c>
+      <c r="H49" s="3">
         <v>25600</v>
-      </c>
-      <c r="H49" s="3">
-        <v>25200</v>
       </c>
       <c r="I49" s="3">
         <v>25200</v>
       </c>
       <c r="J49" s="3">
+        <v>25200</v>
+      </c>
+      <c r="K49" s="3">
         <v>24900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>24600</v>
-      </c>
-      <c r="L49" s="3">
-        <v>24100</v>
       </c>
       <c r="M49" s="3">
         <v>24100</v>
       </c>
       <c r="N49" s="3">
+        <v>24100</v>
+      </c>
+      <c r="O49" s="3">
         <v>24000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>23900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19500</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>19600</v>
       </c>
       <c r="R49" s="3">
         <v>19600</v>
@@ -3365,8 +3476,8 @@
       <c r="T49" s="3">
         <v>19600</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3">
+        <v>19600</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
@@ -3380,8 +3491,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3451,8 +3565,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3522,34 +3639,37 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E52" s="3">
         <v>15300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>8200</v>
       </c>
       <c r="L52" s="3">
         <v>8200</v>
@@ -3558,29 +3678,29 @@
         <v>8200</v>
       </c>
       <c r="N52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="O52" s="3">
         <v>8700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8100</v>
-      </c>
-      <c r="P52" s="3">
-        <v>6000</v>
       </c>
       <c r="Q52" s="3">
         <v>6000</v>
       </c>
       <c r="R52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="S52" s="3">
         <v>6300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3593,8 +3713,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3664,65 +3787,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2370900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2383100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2331600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2312000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2291500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2312100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2327800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2331100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2307500</v>
-      </c>
-      <c r="L54" s="3">
-        <v>2270100</v>
       </c>
       <c r="M54" s="3">
         <v>2270100</v>
       </c>
       <c r="N54" s="3">
+        <v>2270100</v>
+      </c>
+      <c r="O54" s="3">
         <v>2149500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2121800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1983700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1840100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1609800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1476700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1458200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3735,8 +3861,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3762,8 +3891,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3789,65 +3919,66 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2022300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2028400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1974800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1951300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1936400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1954300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1957500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1941900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1917300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1904600</v>
       </c>
       <c r="M57" s="3">
         <v>1904600</v>
       </c>
       <c r="N57" s="3">
+        <v>1904600</v>
+      </c>
+      <c r="O57" s="3">
         <v>1735100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1593600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3860,49 +3991,52 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>44100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1200</v>
-      </c>
-      <c r="F58" s="3">
-        <v>8400</v>
       </c>
       <c r="G58" s="3">
         <v>8400</v>
       </c>
       <c r="H58" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I58" s="3">
         <v>8000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>40900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>18900</v>
-      </c>
-      <c r="L58" s="3">
-        <v>21200</v>
       </c>
       <c r="M58" s="3">
         <v>21200</v>
       </c>
       <c r="N58" s="3">
+        <v>21200</v>
+      </c>
+      <c r="O58" s="3">
         <v>70000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>160000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>24600</v>
       </c>
       <c r="Q58" s="3">
         <v>24600</v>
@@ -3911,13 +4045,13 @@
         <v>24600</v>
       </c>
       <c r="S58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="T58" s="3">
         <v>24500</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>24500</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -3931,8 +4065,11 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3972,12 +4109,12 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>12100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3993,8 +4130,8 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
@@ -4002,50 +4139,53 @@
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2024600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2074200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1977800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1961200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1946700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1963800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1980100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1984500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1938200</v>
-      </c>
-      <c r="L60" s="3">
-        <v>1927500</v>
       </c>
       <c r="M60" s="3">
         <v>1927500</v>
       </c>
       <c r="N60" s="3">
+        <v>1927500</v>
+      </c>
+      <c r="O60" s="3">
         <v>1806900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1754900</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4073,50 +4213,53 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>127600</v>
+      </c>
+      <c r="E61" s="3">
         <v>93000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>136500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>137000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>134600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>134400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>142000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>142600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>164800</v>
-      </c>
-      <c r="L61" s="3">
-        <v>145200</v>
       </c>
       <c r="M61" s="3">
         <v>145200</v>
       </c>
       <c r="N61" s="3">
+        <v>145200</v>
+      </c>
+      <c r="O61" s="3">
         <v>145400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>169800</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4144,50 +4287,53 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E62" s="3">
         <v>15300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>12500</v>
       </c>
       <c r="M62" s="3">
         <v>12500</v>
       </c>
       <c r="N62" s="3">
+        <v>12500</v>
+      </c>
+      <c r="O62" s="3">
         <v>11400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14300</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -4215,8 +4361,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4286,8 +4435,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4357,8 +4509,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4428,65 +4583,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2169500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2182800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2129700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2113100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2094900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2115500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2135500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2141000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2118000</v>
-      </c>
-      <c r="L66" s="3">
-        <v>2085200</v>
       </c>
       <c r="M66" s="3">
         <v>2085200</v>
       </c>
       <c r="N66" s="3">
+        <v>2085200</v>
+      </c>
+      <c r="O66" s="3">
         <v>1963600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1939000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1806100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1667500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1442400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1341900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1328800</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4499,8 +4657,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4526,8 +4687,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4597,8 +4759,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4668,8 +4833,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4695,7 +4863,7 @@
         <v>5000</v>
       </c>
       <c r="K70" s="3">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="L70" s="3">
         <v>3000</v>
@@ -4713,7 +4881,7 @@
         <v>3000</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -4739,8 +4907,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4810,65 +4981,68 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>73500</v>
+      </c>
+      <c r="E72" s="3">
         <v>72400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>73100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>70400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>68700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>67900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>64800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>62000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>61900</v>
-      </c>
-      <c r="L72" s="3">
-        <v>58600</v>
       </c>
       <c r="M72" s="3">
         <v>58600</v>
       </c>
       <c r="N72" s="3">
+        <v>58600</v>
+      </c>
+      <c r="O72" s="3">
         <v>58700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>55900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>51100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>46500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>41400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>36800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>31500</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4881,8 +5055,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4952,8 +5129,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5023,8 +5203,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5094,65 +5277,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>196400</v>
+      </c>
+      <c r="E76" s="3">
         <v>195200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>196800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>193800</v>
-      </c>
-      <c r="G76" s="3">
-        <v>191600</v>
       </c>
       <c r="H76" s="3">
         <v>191600</v>
       </c>
       <c r="I76" s="3">
+        <v>191600</v>
+      </c>
+      <c r="J76" s="3">
         <v>187300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>185000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>186600</v>
-      </c>
-      <c r="L76" s="3">
-        <v>181900</v>
       </c>
       <c r="M76" s="3">
         <v>181900</v>
       </c>
       <c r="N76" s="3">
+        <v>181900</v>
+      </c>
+      <c r="O76" s="3">
         <v>182900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>179800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>174700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>172600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>167400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>134800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>129400</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5165,8 +5351,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5236,70 +5425,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
-      </c>
-      <c r="L80" s="2">
-        <v>45291</v>
       </c>
       <c r="M80" s="2">
         <v>45291</v>
       </c>
       <c r="N80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5312,65 +5504,68 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4100</v>
-      </c>
-      <c r="L81" s="3">
-        <v>3800</v>
       </c>
       <c r="M81" s="3">
         <v>3800</v>
       </c>
       <c r="N81" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O81" s="3">
         <v>3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6500</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5383,8 +5578,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5410,8 +5608,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5419,25 +5618,25 @@
         <v>900</v>
       </c>
       <c r="E83" s="3">
+        <v>900</v>
+      </c>
+      <c r="F83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1000</v>
       </c>
       <c r="H83" s="3">
         <v>1000</v>
       </c>
       <c r="I83" s="3">
-        <v>2100</v>
+        <v>1000</v>
       </c>
       <c r="J83" s="3">
         <v>2100</v>
       </c>
       <c r="K83" s="3">
-        <v>900</v>
+        <v>2100</v>
       </c>
       <c r="L83" s="3">
         <v>900</v>
@@ -5446,10 +5645,10 @@
         <v>900</v>
       </c>
       <c r="N83" s="3">
+        <v>900</v>
+      </c>
+      <c r="O83" s="3">
         <v>800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>400</v>
       </c>
       <c r="P83" s="3">
         <v>400</v>
@@ -5461,7 +5660,7 @@
         <v>400</v>
       </c>
       <c r="S83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -5472,8 +5671,8 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -5481,8 +5680,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5552,8 +5754,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5623,8 +5828,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5694,8 +5902,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5765,8 +5976,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5836,59 +6050,62 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E89" s="3">
         <v>8300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2100</v>
       </c>
-      <c r="G89" s="3">
-        <v>4100</v>
-      </c>
       <c r="H89" s="3">
+        <v>300</v>
+      </c>
+      <c r="I89" s="3">
         <v>5500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3600</v>
-      </c>
-      <c r="L89" s="3">
-        <v>4100</v>
       </c>
       <c r="M89" s="3">
         <v>4100</v>
       </c>
       <c r="N89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O89" s="3">
         <v>900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>7500</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
@@ -5898,8 +6115,8 @@
       <c r="V89" s="3">
         <v>0</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
@@ -5907,8 +6124,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5934,8 +6154,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5943,50 +6164,50 @@
         <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-400</v>
       </c>
       <c r="M91" s="3">
         <v>-400</v>
       </c>
       <c r="N91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -5996,8 +6217,8 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6005,8 +6226,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6076,8 +6300,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6147,59 +6374,62 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7700</v>
       </c>
-      <c r="G94" s="3">
-        <v>13000</v>
-      </c>
       <c r="H94" s="3">
+        <v>16900</v>
+      </c>
+      <c r="I94" s="3">
         <v>38300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>8800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-76200</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-137400</v>
       </c>
       <c r="M94" s="3">
         <v>-137400</v>
       </c>
       <c r="N94" s="3">
+        <v>-137400</v>
+      </c>
+      <c r="O94" s="3">
         <v>-46600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-43400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-129400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-214700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-128300</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -6209,8 +6439,8 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
@@ -6218,8 +6448,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6245,25 +6478,26 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3">
         <v>800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>800</v>
       </c>
-      <c r="G96" s="3">
-        <v>700</v>
-      </c>
-      <c r="H96" s="3">
-        <v>700</v>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I96" s="3">
         <v>700</v>
@@ -6287,7 +6521,7 @@
         <v>700</v>
       </c>
       <c r="P96" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="Q96" s="3">
         <v>-700</v>
@@ -6296,7 +6530,7 @@
         <v>-700</v>
       </c>
       <c r="S96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="T96" s="3">
         <v>0</v>
@@ -6316,8 +6550,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6387,8 +6624,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6458,8 +6698,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6529,59 +6772,62 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E100" s="3">
         <v>51500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>15200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>14100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-19800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-22200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>24100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>31900</v>
-      </c>
-      <c r="L100" s="3">
-        <v>117800</v>
       </c>
       <c r="M100" s="3">
         <v>117800</v>
       </c>
       <c r="N100" s="3">
+        <v>117800</v>
+      </c>
+      <c r="O100" s="3">
         <v>26800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>42600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>125600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>222900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>127700</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -6591,8 +6837,8 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
+      <c r="W100" s="3">
+        <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
@@ -6600,8 +6846,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6641,8 +6890,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6671,59 +6920,62 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E102" s="3">
         <v>41300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>21600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-40700</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-15400</v>
       </c>
       <c r="M102" s="3">
         <v>-15400</v>
       </c>
       <c r="N102" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="O102" s="3">
         <v>-18900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>16000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6800</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
@@ -6733,13 +6985,16 @@
       <c r="V102" s="3">
         <v>0</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
